--- a/Data/ON_Market.xlsx
+++ b/Data/ON_Market.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4AF23A8-5329-4D71-B0AD-083E900F5DCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEE7A519-CC33-4CE7-B37A-565E9EBB6C4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11550" yWindow="390" windowWidth="8520" windowHeight="10605" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30" yWindow="135" windowWidth="8520" windowHeight="10605" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settlement" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="40">
   <si>
     <t>ExchangeMaster</t>
   </si>
@@ -39,20 +39,119 @@
     <t>settlement_Year</t>
   </si>
   <si>
-    <t>expiry_Date</t>
-  </si>
-  <si>
-    <t>trade_Start_Date</t>
-  </si>
-  <si>
     <t>11 - MCX</t>
+  </si>
+  <si>
+    <t>expectedDay</t>
+  </si>
+  <si>
+    <t>expectedMonth</t>
+  </si>
+  <si>
+    <t>expectedYear</t>
+  </si>
+  <si>
+    <t>October</t>
+  </si>
+  <si>
+    <t>trade_Day</t>
+  </si>
+  <si>
+    <t>trade_Month</t>
+  </si>
+  <si>
+    <t>trade_Year</t>
+  </si>
+  <si>
+    <t>PostExpiry_Validity_Date</t>
+  </si>
+  <si>
+    <t>PostExpiry_Validity_Month</t>
+  </si>
+  <si>
+    <t>PostExpiry_Validity_Year</t>
+  </si>
+  <si>
+    <t>Delivery_Marking</t>
+  </si>
+  <si>
+    <t>Delivery_Marking_Month</t>
+  </si>
+  <si>
+    <t>Delivery_Marking_Year</t>
+  </si>
+  <si>
+    <t>commodity</t>
+  </si>
+  <si>
+    <t>15 - COTTON BALES</t>
+  </si>
+  <si>
+    <t>pay_In_date</t>
+  </si>
+  <si>
+    <t>pay_In_Month</t>
+  </si>
+  <si>
+    <t>pay_In_Year</t>
+  </si>
+  <si>
+    <t>pay_In_Date_hr</t>
+  </si>
+  <si>
+    <t>pay_In_Date_mn</t>
+  </si>
+  <si>
+    <t>pay_out_date</t>
+  </si>
+  <si>
+    <t>pay_out_Month</t>
+  </si>
+  <si>
+    <t>pay_out_Year</t>
+  </si>
+  <si>
+    <t>pay_out_Date_hr</t>
+  </si>
+  <si>
+    <t>pay_out_Date_mn</t>
+  </si>
+  <si>
+    <t>early_pay_In_date</t>
+  </si>
+  <si>
+    <t>early_pay_In_Month</t>
+  </si>
+  <si>
+    <t>early_pay_In_Year</t>
+  </si>
+  <si>
+    <t>early_pay_In_Date_hr</t>
+  </si>
+  <si>
+    <t>early_pay_In_Date_mn</t>
+  </si>
+  <si>
+    <t>early_Payin_End_date</t>
+  </si>
+  <si>
+    <t>early_Payin_End_Month</t>
+  </si>
+  <si>
+    <t>early_Payin_End_Year</t>
+  </si>
+  <si>
+    <t>early_Payin_End_Date_hr</t>
+  </si>
+  <si>
+    <t>early_Payin_End_Date_mn</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -69,12 +168,6 @@
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF2A00FF"/>
-      <name val="Consolas"/>
-      <family val="3"/>
-    </font>
-    <font>
-      <sz val="10"/>
       <name val="Consolas"/>
       <family val="3"/>
     </font>
@@ -83,6 +176,32 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="3">
@@ -99,7 +218,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -122,18 +241,39 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -414,18 +554,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:DN7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.140625" customWidth="1"/>
+    <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:118" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -439,55 +581,897 @@
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="K1" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="L1" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="N1" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="O1" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="P1" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q1" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="U1" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="V1" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="W1" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y1" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AG1" s="1"/>
+      <c r="AH1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AI1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AJ1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AK1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AL1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AM1" s="1"/>
+      <c r="AN1" s="1"/>
+      <c r="AO1" s="1"/>
+      <c r="AP1" s="1"/>
+      <c r="AQ1" s="1"/>
+      <c r="AR1" s="1"/>
+      <c r="AS1" s="1"/>
+      <c r="AT1" s="1"/>
+      <c r="AU1" s="1"/>
+      <c r="AV1" s="1"/>
+      <c r="AW1" s="1"/>
+      <c r="AX1" s="1"/>
+      <c r="AY1" s="1"/>
+      <c r="AZ1" s="1"/>
+      <c r="BA1" s="1"/>
+      <c r="BB1" s="1"/>
+      <c r="BC1" s="1"/>
+      <c r="BD1" s="1"/>
+      <c r="BE1" s="1"/>
+      <c r="BF1" s="1"/>
+      <c r="BG1" s="1"/>
+      <c r="BH1" s="1"/>
+      <c r="BI1" s="1"/>
+      <c r="BJ1" s="1"/>
+      <c r="BK1" s="1"/>
+      <c r="BL1" s="1"/>
+      <c r="BM1" s="1"/>
+      <c r="BN1" s="1"/>
+      <c r="BO1" s="1"/>
+      <c r="BP1" s="1"/>
+      <c r="BQ1" s="1"/>
+      <c r="BR1" s="1"/>
+      <c r="BS1" s="1"/>
+      <c r="BT1" s="1"/>
+      <c r="BU1" s="1"/>
+      <c r="BV1" s="1"/>
+      <c r="BW1" s="1"/>
+      <c r="BX1" s="1"/>
+      <c r="BY1" s="1"/>
+      <c r="BZ1" s="1"/>
+      <c r="CA1" s="1"/>
+      <c r="CB1" s="1"/>
+      <c r="CC1" s="1"/>
+      <c r="CD1" s="1"/>
+      <c r="CE1" s="1"/>
+      <c r="CF1" s="1"/>
+      <c r="CG1" s="1"/>
+      <c r="CH1" s="1"/>
+      <c r="CI1" s="1"/>
+      <c r="CJ1" s="1"/>
+      <c r="CK1" s="1"/>
+      <c r="CL1" s="1"/>
+      <c r="CM1" s="1"/>
+      <c r="CN1" s="1"/>
+      <c r="CO1" s="1"/>
+      <c r="CP1" s="1"/>
+      <c r="CQ1" s="1"/>
+      <c r="CR1" s="1"/>
+      <c r="CS1" s="1"/>
+      <c r="CT1" s="1"/>
+      <c r="CU1" s="1"/>
+      <c r="CV1" s="1"/>
+      <c r="CW1" s="1"/>
+      <c r="CX1" s="1"/>
+      <c r="CY1" s="1"/>
+      <c r="CZ1" s="1"/>
+      <c r="DA1" s="1"/>
+      <c r="DB1" s="1"/>
+      <c r="DC1" s="1"/>
+      <c r="DD1" s="1"/>
+      <c r="DE1" s="1"/>
+      <c r="DF1" s="1"/>
+      <c r="DG1" s="1"/>
+      <c r="DH1" s="1"/>
+      <c r="DI1" s="1"/>
+      <c r="DJ1" s="1"/>
+      <c r="DK1" s="1"/>
+      <c r="DL1" s="1"/>
+      <c r="DM1" s="1"/>
+      <c r="DN1" s="1"/>
+    </row>
+    <row r="2" spans="1:118" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
-      </c>
+      <c r="B2" s="4">
+        <v>92</v>
+      </c>
+      <c r="C2" s="4">
+        <v>113</v>
+      </c>
+      <c r="D2" s="4">
+        <v>2025</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2" s="6">
+        <v>1</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="8">
+        <v>2025</v>
+      </c>
+      <c r="I2" s="1">
+        <v>19</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K2" s="1">
+        <v>2025</v>
+      </c>
+      <c r="L2" s="1">
+        <v>30</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="N2" s="1">
+        <v>2025</v>
+      </c>
+      <c r="O2" s="1">
+        <v>15</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q2" s="1">
+        <v>2025</v>
+      </c>
+      <c r="R2" s="1"/>
+      <c r="S2" s="1"/>
+      <c r="T2" s="1"/>
+      <c r="U2" s="14"/>
+      <c r="V2" s="1"/>
+      <c r="W2" s="1"/>
+      <c r="X2" s="1"/>
+      <c r="Y2" s="1"/>
+      <c r="Z2" s="1"/>
+      <c r="AA2" s="1"/>
+      <c r="AB2" s="1"/>
+      <c r="AC2" s="1"/>
+      <c r="AD2" s="1"/>
+      <c r="AE2" s="1"/>
+      <c r="AF2" s="1"/>
+      <c r="AG2" s="1"/>
+      <c r="AH2" s="1"/>
+      <c r="AI2" s="1"/>
+      <c r="AJ2" s="1"/>
+      <c r="AK2" s="1"/>
+      <c r="AL2" s="1"/>
+      <c r="AM2" s="1"/>
+      <c r="AN2" s="1"/>
+      <c r="AO2" s="1"/>
+      <c r="AP2" s="1"/>
+      <c r="AQ2" s="1"/>
+      <c r="AR2" s="1"/>
+      <c r="AS2" s="1"/>
+      <c r="AT2" s="1"/>
+      <c r="AU2" s="1"/>
+      <c r="AV2" s="1"/>
+      <c r="AW2" s="1"/>
+      <c r="AX2" s="1"/>
+      <c r="AY2" s="1"/>
+      <c r="AZ2" s="1"/>
+      <c r="BA2" s="1"/>
+      <c r="BB2" s="1"/>
+      <c r="BC2" s="1"/>
+      <c r="BD2" s="1"/>
+      <c r="BE2" s="1"/>
+      <c r="BF2" s="1"/>
+      <c r="BG2" s="1"/>
+      <c r="BH2" s="1"/>
+      <c r="BI2" s="1"/>
+      <c r="BJ2" s="1"/>
+      <c r="BK2" s="1"/>
+      <c r="BL2" s="1"/>
+      <c r="BM2" s="1"/>
+      <c r="BN2" s="1"/>
+      <c r="BO2" s="1"/>
+      <c r="BP2" s="1"/>
+      <c r="BQ2" s="1"/>
+      <c r="BR2" s="1"/>
+      <c r="BS2" s="1"/>
+      <c r="BT2" s="1"/>
+      <c r="BU2" s="1"/>
+      <c r="BV2" s="1"/>
+      <c r="BW2" s="1"/>
+      <c r="BX2" s="1"/>
+      <c r="BY2" s="1"/>
+      <c r="BZ2" s="1"/>
+      <c r="CA2" s="1"/>
+      <c r="CB2" s="1"/>
+      <c r="CC2" s="1"/>
+      <c r="CD2" s="1"/>
+      <c r="CE2" s="1"/>
+      <c r="CF2" s="1"/>
+      <c r="CG2" s="1"/>
+      <c r="CH2" s="1"/>
+      <c r="CI2" s="1"/>
+      <c r="CJ2" s="1"/>
+      <c r="CK2" s="1"/>
+      <c r="CL2" s="1"/>
+      <c r="CM2" s="1"/>
+      <c r="CN2" s="1"/>
+      <c r="CO2" s="1"/>
+      <c r="CP2" s="1"/>
+      <c r="CQ2" s="1"/>
+      <c r="CR2" s="1"/>
+      <c r="CS2" s="1"/>
+      <c r="CT2" s="1"/>
+      <c r="CU2" s="1"/>
+      <c r="CV2" s="1"/>
+      <c r="CW2" s="1"/>
+      <c r="CX2" s="1"/>
+      <c r="CY2" s="1"/>
+      <c r="CZ2" s="1"/>
+      <c r="DA2" s="1"/>
+      <c r="DB2" s="1"/>
+      <c r="DC2" s="1"/>
+      <c r="DD2" s="1"/>
+      <c r="DE2" s="1"/>
+      <c r="DF2" s="1"/>
+      <c r="DG2" s="1"/>
+      <c r="DH2" s="1"/>
+      <c r="DI2" s="1"/>
+      <c r="DJ2" s="1"/>
+      <c r="DK2" s="1"/>
+      <c r="DL2" s="1"/>
+      <c r="DM2" s="1"/>
+      <c r="DN2" s="1"/>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="5">
-        <v>92</v>
-      </c>
-      <c r="C2" s="5">
-        <v>113</v>
-      </c>
-      <c r="D2" s="5">
-        <v>2025</v>
-      </c>
-      <c r="E2" s="6">
-        <v>45926</v>
-      </c>
-      <c r="F2" s="3">
-        <v>45930</v>
-      </c>
+    <row r="3" spans="1:118" x14ac:dyDescent="0.25">
+      <c r="A3" s="4"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="1"/>
+      <c r="N3" s="1"/>
+      <c r="O3" s="1"/>
+      <c r="P3" s="1"/>
+      <c r="Q3" s="1"/>
+      <c r="R3" s="1"/>
+      <c r="S3" s="1"/>
+      <c r="T3" s="1"/>
+      <c r="U3" s="14"/>
+      <c r="V3" s="1"/>
+      <c r="W3" s="1"/>
+      <c r="X3" s="1"/>
+      <c r="Y3" s="1"/>
+      <c r="Z3" s="1"/>
+      <c r="AA3" s="1"/>
+      <c r="AB3" s="1"/>
+      <c r="AC3" s="1"/>
+      <c r="AD3" s="1"/>
+      <c r="AE3" s="1"/>
+      <c r="AF3" s="1"/>
+      <c r="AG3" s="1"/>
+      <c r="AH3" s="1"/>
+      <c r="AI3" s="1"/>
+      <c r="AJ3" s="1"/>
+      <c r="AK3" s="1"/>
+      <c r="AL3" s="1"/>
+      <c r="AM3" s="1"/>
+      <c r="AN3" s="1"/>
+      <c r="AO3" s="1"/>
+      <c r="AP3" s="1"/>
+      <c r="AQ3" s="1"/>
+      <c r="AR3" s="1"/>
+      <c r="AS3" s="1"/>
+      <c r="AT3" s="1"/>
+      <c r="AU3" s="1"/>
+      <c r="AV3" s="1"/>
+      <c r="AW3" s="1"/>
+      <c r="AX3" s="1"/>
+      <c r="AY3" s="1"/>
+      <c r="AZ3" s="1"/>
+      <c r="BA3" s="1"/>
+      <c r="BB3" s="1"/>
+      <c r="BC3" s="1"/>
+      <c r="BD3" s="1"/>
+      <c r="BE3" s="1"/>
+      <c r="BF3" s="1"/>
+      <c r="BG3" s="1"/>
+      <c r="BH3" s="1"/>
+      <c r="BI3" s="1"/>
+      <c r="BJ3" s="1"/>
+      <c r="BK3" s="1"/>
+      <c r="BL3" s="1"/>
+      <c r="BM3" s="1"/>
+      <c r="BN3" s="1"/>
+      <c r="BO3" s="1"/>
+      <c r="BP3" s="1"/>
+      <c r="BQ3" s="1"/>
+      <c r="BR3" s="1"/>
+      <c r="BS3" s="1"/>
+      <c r="BT3" s="1"/>
+      <c r="BU3" s="1"/>
+      <c r="BV3" s="1"/>
+      <c r="BW3" s="1"/>
+      <c r="BX3" s="1"/>
+      <c r="BY3" s="1"/>
+      <c r="BZ3" s="1"/>
+      <c r="CA3" s="1"/>
+      <c r="CB3" s="1"/>
+      <c r="CC3" s="1"/>
+      <c r="CD3" s="1"/>
+      <c r="CE3" s="1"/>
+      <c r="CF3" s="1"/>
+      <c r="CG3" s="1"/>
+      <c r="CH3" s="1"/>
+      <c r="CI3" s="1"/>
+      <c r="CJ3" s="1"/>
+      <c r="CK3" s="1"/>
+      <c r="CL3" s="1"/>
+      <c r="CM3" s="1"/>
+      <c r="CN3" s="1"/>
+      <c r="CO3" s="1"/>
+      <c r="CP3" s="1"/>
+      <c r="CQ3" s="1"/>
+      <c r="CR3" s="1"/>
+      <c r="CS3" s="1"/>
+      <c r="CT3" s="1"/>
+      <c r="CU3" s="1"/>
+      <c r="CV3" s="1"/>
+      <c r="CW3" s="1"/>
+      <c r="CX3" s="1"/>
+      <c r="CY3" s="1"/>
+      <c r="CZ3" s="1"/>
+      <c r="DA3" s="1"/>
+      <c r="DB3" s="1"/>
+      <c r="DC3" s="1"/>
+      <c r="DD3" s="1"/>
+      <c r="DE3" s="1"/>
+      <c r="DF3" s="1"/>
+      <c r="DG3" s="1"/>
+      <c r="DH3" s="1"/>
+      <c r="DI3" s="1"/>
+      <c r="DJ3" s="1"/>
+      <c r="DK3" s="1"/>
+      <c r="DL3" s="1"/>
+      <c r="DM3" s="1"/>
+      <c r="DN3" s="1"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="5"/>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="1"/>
+    <row r="4" spans="1:118" x14ac:dyDescent="0.25">
+      <c r="A4" s="4"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+      <c r="N4" s="1"/>
+      <c r="O4" s="1"/>
+      <c r="P4" s="1"/>
+      <c r="Q4" s="1"/>
+      <c r="R4" s="1"/>
+      <c r="S4" s="1"/>
+      <c r="T4" s="1"/>
+      <c r="U4" s="14"/>
+      <c r="V4" s="1"/>
+      <c r="W4" s="1"/>
+      <c r="X4" s="1"/>
+      <c r="Y4" s="1"/>
+      <c r="Z4" s="1"/>
+      <c r="AA4" s="1"/>
+      <c r="AB4" s="1"/>
+      <c r="AC4" s="1"/>
+      <c r="AD4" s="1"/>
+      <c r="AE4" s="1"/>
+      <c r="AF4" s="1"/>
+      <c r="AG4" s="1"/>
+      <c r="AH4" s="1"/>
+      <c r="AI4" s="1"/>
+      <c r="AJ4" s="1"/>
+      <c r="AK4" s="1"/>
+      <c r="AL4" s="1"/>
+      <c r="AM4" s="1"/>
+      <c r="AN4" s="1"/>
+      <c r="AO4" s="1"/>
+      <c r="AP4" s="1"/>
+      <c r="AQ4" s="1"/>
+      <c r="AR4" s="1"/>
+      <c r="AS4" s="1"/>
+      <c r="AT4" s="1"/>
+      <c r="AU4" s="1"/>
+      <c r="AV4" s="1"/>
+      <c r="AW4" s="1"/>
+      <c r="AX4" s="1"/>
+      <c r="AY4" s="1"/>
+      <c r="AZ4" s="1"/>
+      <c r="BA4" s="1"/>
+      <c r="BB4" s="1"/>
+      <c r="BC4" s="1"/>
+      <c r="BD4" s="1"/>
+      <c r="BE4" s="1"/>
+      <c r="BF4" s="1"/>
+      <c r="BG4" s="1"/>
+      <c r="BH4" s="1"/>
+      <c r="BI4" s="1"/>
+      <c r="BJ4" s="1"/>
+      <c r="BK4" s="1"/>
+      <c r="BL4" s="1"/>
+      <c r="BM4" s="1"/>
+      <c r="BN4" s="1"/>
+      <c r="BO4" s="1"/>
+      <c r="BP4" s="1"/>
+      <c r="BQ4" s="1"/>
+      <c r="BR4" s="1"/>
+      <c r="BS4" s="1"/>
+      <c r="BT4" s="1"/>
+      <c r="BU4" s="1"/>
+      <c r="BV4" s="1"/>
+      <c r="BW4" s="1"/>
+      <c r="BX4" s="1"/>
+      <c r="BY4" s="1"/>
+      <c r="BZ4" s="1"/>
+      <c r="CA4" s="1"/>
+      <c r="CB4" s="1"/>
+      <c r="CC4" s="1"/>
+      <c r="CD4" s="1"/>
+      <c r="CE4" s="1"/>
+      <c r="CF4" s="1"/>
+      <c r="CG4" s="1"/>
+      <c r="CH4" s="1"/>
+      <c r="CI4" s="1"/>
+      <c r="CJ4" s="1"/>
+      <c r="CK4" s="1"/>
+      <c r="CL4" s="1"/>
+      <c r="CM4" s="1"/>
+      <c r="CN4" s="1"/>
+      <c r="CO4" s="1"/>
+      <c r="CP4" s="1"/>
+      <c r="CQ4" s="1"/>
+      <c r="CR4" s="1"/>
+      <c r="CS4" s="1"/>
+      <c r="CT4" s="1"/>
+      <c r="CU4" s="1"/>
+      <c r="CV4" s="1"/>
+      <c r="CW4" s="1"/>
+      <c r="CX4" s="1"/>
+      <c r="CY4" s="1"/>
+      <c r="CZ4" s="1"/>
+      <c r="DA4" s="1"/>
+      <c r="DB4" s="1"/>
+      <c r="DC4" s="1"/>
+      <c r="DD4" s="1"/>
+      <c r="DE4" s="1"/>
+      <c r="DF4" s="1"/>
+      <c r="DG4" s="1"/>
+      <c r="DH4" s="1"/>
+      <c r="DI4" s="1"/>
+      <c r="DJ4" s="1"/>
+      <c r="DK4" s="1"/>
+      <c r="DL4" s="1"/>
+      <c r="DM4" s="1"/>
+      <c r="DN4" s="1"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="5"/>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="1"/>
+    <row r="5" spans="1:118" x14ac:dyDescent="0.25">
+      <c r="A5" s="4"/>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="1"/>
+      <c r="N5" s="1"/>
+      <c r="O5" s="1"/>
+      <c r="P5" s="1"/>
+      <c r="Q5" s="1"/>
+      <c r="R5" s="1"/>
+      <c r="S5" s="1"/>
+      <c r="T5" s="1"/>
+      <c r="U5" s="14"/>
+      <c r="V5" s="1"/>
+      <c r="W5" s="1"/>
+      <c r="X5" s="1"/>
+      <c r="Y5" s="1"/>
+      <c r="Z5" s="1"/>
+      <c r="AA5" s="1"/>
+      <c r="AB5" s="1"/>
+      <c r="AC5" s="1"/>
+      <c r="AD5" s="1"/>
+      <c r="AE5" s="1"/>
+      <c r="AF5" s="1"/>
+      <c r="AG5" s="1"/>
+      <c r="AH5" s="1"/>
+      <c r="AI5" s="1"/>
+      <c r="AJ5" s="1"/>
+      <c r="AK5" s="1"/>
+      <c r="AL5" s="1"/>
+      <c r="AM5" s="1"/>
+      <c r="AN5" s="1"/>
+      <c r="AO5" s="1"/>
+      <c r="AP5" s="1"/>
+      <c r="AQ5" s="1"/>
+      <c r="AR5" s="1"/>
+      <c r="AS5" s="1"/>
+      <c r="AT5" s="1"/>
+      <c r="AU5" s="1"/>
+      <c r="AV5" s="1"/>
+      <c r="AW5" s="1"/>
+      <c r="AX5" s="1"/>
+      <c r="AY5" s="1"/>
+      <c r="AZ5" s="1"/>
+      <c r="BA5" s="1"/>
+      <c r="BB5" s="1"/>
+      <c r="BC5" s="1"/>
+      <c r="BD5" s="1"/>
+      <c r="BE5" s="1"/>
+      <c r="BF5" s="1"/>
+      <c r="BG5" s="1"/>
+      <c r="BH5" s="1"/>
+      <c r="BI5" s="1"/>
+      <c r="BJ5" s="1"/>
+      <c r="BK5" s="1"/>
+      <c r="BL5" s="1"/>
+      <c r="BM5" s="1"/>
+      <c r="BN5" s="1"/>
+      <c r="BO5" s="1"/>
+      <c r="BP5" s="1"/>
+      <c r="BQ5" s="1"/>
+      <c r="BR5" s="1"/>
+      <c r="BS5" s="1"/>
+      <c r="BT5" s="1"/>
+      <c r="BU5" s="1"/>
+      <c r="BV5" s="1"/>
+      <c r="BW5" s="1"/>
+      <c r="BX5" s="1"/>
+      <c r="BY5" s="1"/>
+      <c r="BZ5" s="1"/>
+      <c r="CA5" s="1"/>
+      <c r="CB5" s="1"/>
+      <c r="CC5" s="1"/>
+      <c r="CD5" s="1"/>
+      <c r="CE5" s="1"/>
+      <c r="CF5" s="1"/>
+      <c r="CG5" s="1"/>
+      <c r="CH5" s="1"/>
+      <c r="CI5" s="1"/>
+      <c r="CJ5" s="1"/>
+      <c r="CK5" s="1"/>
+      <c r="CL5" s="1"/>
+      <c r="CM5" s="1"/>
+      <c r="CN5" s="1"/>
+      <c r="CO5" s="1"/>
+      <c r="CP5" s="1"/>
+      <c r="CQ5" s="1"/>
+      <c r="CR5" s="1"/>
+      <c r="CS5" s="1"/>
+      <c r="CT5" s="1"/>
+      <c r="CU5" s="1"/>
+      <c r="CV5" s="1"/>
+      <c r="CW5" s="1"/>
+      <c r="CX5" s="1"/>
+      <c r="CY5" s="1"/>
+      <c r="CZ5" s="1"/>
+      <c r="DA5" s="1"/>
+      <c r="DB5" s="1"/>
+      <c r="DC5" s="1"/>
+      <c r="DD5" s="1"/>
+      <c r="DE5" s="1"/>
+      <c r="DF5" s="1"/>
+      <c r="DG5" s="1"/>
+      <c r="DH5" s="1"/>
+      <c r="DI5" s="1"/>
+      <c r="DJ5" s="1"/>
+      <c r="DK5" s="1"/>
+      <c r="DL5" s="1"/>
+      <c r="DM5" s="1"/>
+      <c r="DN5" s="1"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="5"/>
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="1"/>
+    <row r="6" spans="1:118" x14ac:dyDescent="0.25">
+      <c r="V6" s="1"/>
+      <c r="W6" s="1"/>
+      <c r="X6" s="1"/>
+      <c r="Y6" s="1"/>
+      <c r="Z6" s="1"/>
+      <c r="AA6" s="1"/>
+      <c r="AB6" s="1"/>
+      <c r="AC6" s="1"/>
+      <c r="AD6" s="1"/>
+      <c r="AE6" s="1"/>
+      <c r="AF6" s="1"/>
+      <c r="AG6" s="1"/>
+      <c r="AH6" s="1"/>
+      <c r="AI6" s="1"/>
+      <c r="AJ6" s="1"/>
+      <c r="AK6" s="1"/>
+      <c r="AL6" s="1"/>
+      <c r="AM6" s="1"/>
+      <c r="AN6" s="1"/>
+      <c r="AO6" s="1"/>
+      <c r="AP6" s="1"/>
+      <c r="AQ6" s="1"/>
+      <c r="AR6" s="1"/>
+      <c r="AS6" s="1"/>
+      <c r="AT6" s="1"/>
+      <c r="AU6" s="1"/>
+      <c r="AV6" s="1"/>
+      <c r="AW6" s="1"/>
+      <c r="AX6" s="1"/>
+      <c r="AY6" s="1"/>
+      <c r="AZ6" s="1"/>
+      <c r="BA6" s="1"/>
+      <c r="BB6" s="1"/>
+      <c r="BC6" s="1"/>
+      <c r="BD6" s="1"/>
+      <c r="BE6" s="1"/>
+      <c r="BF6" s="1"/>
+      <c r="BG6" s="1"/>
+      <c r="BH6" s="1"/>
+      <c r="BI6" s="1"/>
+      <c r="BJ6" s="1"/>
+      <c r="BK6" s="1"/>
+      <c r="BL6" s="1"/>
+      <c r="BM6" s="1"/>
+      <c r="BN6" s="1"/>
+      <c r="BO6" s="1"/>
+      <c r="BP6" s="1"/>
+      <c r="BQ6" s="1"/>
+      <c r="BR6" s="1"/>
+      <c r="BS6" s="1"/>
+      <c r="BT6" s="1"/>
+      <c r="BU6" s="1"/>
+      <c r="BV6" s="1"/>
+      <c r="BW6" s="1"/>
+      <c r="BX6" s="1"/>
+      <c r="BY6" s="1"/>
+      <c r="BZ6" s="1"/>
+      <c r="CA6" s="1"/>
+      <c r="CB6" s="1"/>
+      <c r="CC6" s="1"/>
+      <c r="CD6" s="1"/>
+      <c r="CE6" s="1"/>
+      <c r="CF6" s="1"/>
+      <c r="CG6" s="1"/>
+      <c r="CH6" s="1"/>
+      <c r="CI6" s="1"/>
+      <c r="CJ6" s="1"/>
+      <c r="CK6" s="1"/>
+      <c r="CL6" s="1"/>
+      <c r="CM6" s="1"/>
+      <c r="CN6" s="1"/>
+      <c r="CO6" s="1"/>
+      <c r="CP6" s="1"/>
+      <c r="CQ6" s="1"/>
+      <c r="CR6" s="1"/>
+      <c r="CS6" s="1"/>
+      <c r="CT6" s="1"/>
+      <c r="CU6" s="1"/>
+      <c r="CV6" s="1"/>
+      <c r="CW6" s="1"/>
+      <c r="CX6" s="1"/>
+      <c r="CY6" s="1"/>
+      <c r="CZ6" s="1"/>
+      <c r="DA6" s="1"/>
+      <c r="DB6" s="1"/>
+      <c r="DC6" s="1"/>
+      <c r="DD6" s="1"/>
+      <c r="DE6" s="1"/>
+      <c r="DF6" s="1"/>
+      <c r="DG6" s="1"/>
+      <c r="DH6" s="1"/>
+      <c r="DI6" s="1"/>
+      <c r="DJ6" s="1"/>
+      <c r="DK6" s="1"/>
+      <c r="DL6" s="1"/>
+      <c r="DM6" s="1"/>
+      <c r="DN6" s="1"/>
+    </row>
+    <row r="7" spans="1:118" x14ac:dyDescent="0.25">
+      <c r="V7" s="1"/>
+      <c r="W7" s="1"/>
+      <c r="X7" s="1"/>
+      <c r="Y7" s="1"/>
+      <c r="Z7" s="1"/>
+      <c r="AA7" s="1"/>
+      <c r="AB7" s="1"/>
+      <c r="AC7" s="1"/>
+      <c r="AD7" s="1"/>
+      <c r="AE7" s="1"/>
+      <c r="AF7" s="1"/>
+      <c r="AG7" s="1"/>
+      <c r="AH7" s="1"/>
+      <c r="AI7" s="1"/>
+      <c r="AJ7" s="1"/>
+      <c r="AK7" s="1"/>
+      <c r="AL7" s="1"/>
+      <c r="AM7" s="1"/>
+      <c r="AN7" s="1"/>
+      <c r="AO7" s="1"/>
+      <c r="AP7" s="1"/>
+      <c r="AQ7" s="1"/>
+      <c r="AR7" s="1"/>
+      <c r="AS7" s="1"/>
+      <c r="AT7" s="1"/>
+      <c r="AU7" s="1"/>
+      <c r="AV7" s="1"/>
+      <c r="AW7" s="1"/>
+      <c r="AX7" s="1"/>
+      <c r="AY7" s="1"/>
+      <c r="AZ7" s="1"/>
+      <c r="BA7" s="1"/>
+      <c r="BB7" s="1"/>
+      <c r="BC7" s="1"/>
+      <c r="BD7" s="1"/>
+      <c r="BE7" s="1"/>
+      <c r="BF7" s="1"/>
+      <c r="BG7" s="1"/>
+      <c r="BH7" s="1"/>
+      <c r="BI7" s="1"/>
+      <c r="BJ7" s="1"/>
+      <c r="BK7" s="1"/>
+      <c r="BL7" s="1"/>
+      <c r="BM7" s="1"/>
+      <c r="BN7" s="1"/>
+      <c r="BO7" s="1"/>
+      <c r="BP7" s="1"/>
+      <c r="BQ7" s="1"/>
+      <c r="BR7" s="1"/>
+      <c r="BS7" s="1"/>
+      <c r="BT7" s="1"/>
+      <c r="BU7" s="1"/>
+      <c r="BV7" s="1"/>
+      <c r="BW7" s="1"/>
+      <c r="BX7" s="1"/>
+      <c r="BY7" s="1"/>
+      <c r="BZ7" s="1"/>
+      <c r="CA7" s="1"/>
+      <c r="CB7" s="1"/>
+      <c r="CC7" s="1"/>
+      <c r="CD7" s="1"/>
+      <c r="CE7" s="1"/>
+      <c r="CF7" s="1"/>
+      <c r="CG7" s="1"/>
+      <c r="CH7" s="1"/>
+      <c r="CI7" s="1"/>
+      <c r="CJ7" s="1"/>
+      <c r="CK7" s="1"/>
+      <c r="CL7" s="1"/>
+      <c r="CM7" s="1"/>
+      <c r="CN7" s="1"/>
+      <c r="CO7" s="1"/>
+      <c r="CP7" s="1"/>
+      <c r="CQ7" s="1"/>
+      <c r="CR7" s="1"/>
+      <c r="CS7" s="1"/>
+      <c r="CT7" s="1"/>
+      <c r="CU7" s="1"/>
+      <c r="CV7" s="1"/>
+      <c r="CW7" s="1"/>
+      <c r="CX7" s="1"/>
+      <c r="CY7" s="1"/>
+      <c r="CZ7" s="1"/>
+      <c r="DA7" s="1"/>
+      <c r="DB7" s="1"/>
+      <c r="DC7" s="1"/>
+      <c r="DD7" s="1"/>
+      <c r="DE7" s="1"/>
+      <c r="DF7" s="1"/>
+      <c r="DG7" s="1"/>
+      <c r="DH7" s="1"/>
+      <c r="DI7" s="1"/>
+      <c r="DJ7" s="1"/>
+      <c r="DK7" s="1"/>
+      <c r="DL7" s="1"/>
+      <c r="DM7" s="1"/>
+      <c r="DN7" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Data/ON_Market.xlsx
+++ b/Data/ON_Market.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEE7A519-CC33-4CE7-B37A-565E9EBB6C4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D19D67FC-3192-44D9-800A-6A49291FA31A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30" yWindow="135" windowWidth="8520" windowHeight="10605" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11550" yWindow="105" windowWidth="8520" windowHeight="10605" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settlement" sheetId="1" r:id="rId1"/>
+    <sheet name="OnMarket" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="51">
   <si>
     <t>ExchangeMaster</t>
   </si>
@@ -39,9 +40,6 @@
     <t>settlement_Year</t>
   </si>
   <si>
-    <t>11 - MCX</t>
-  </si>
-  <si>
     <t>expectedDay</t>
   </si>
   <si>
@@ -145,13 +143,49 @@
   </si>
   <si>
     <t>early_Payin_End_Date_mn</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 11 - MCX</t>
+  </si>
+  <si>
+    <t>PayinType</t>
+  </si>
+  <si>
+    <t>Instr_Slip_No</t>
+  </si>
+  <si>
+    <t>WSP_Id</t>
+  </si>
+  <si>
+    <t>WH_Id</t>
+  </si>
+  <si>
+    <t>Commodity</t>
+  </si>
+  <si>
+    <t>Client_Id</t>
+  </si>
+  <si>
+    <t>UCC_Id</t>
+  </si>
+  <si>
+    <t>TM_Id</t>
+  </si>
+  <si>
+    <t>CM_Id</t>
+  </si>
+  <si>
+    <t>Settlement_No</t>
+  </si>
+  <si>
+    <t>ENWR_No</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -203,8 +237,16 @@
       <name val="Consolas"/>
       <family val="3"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -214,6 +256,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -267,13 +315,13 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -581,104 +629,104 @@
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="H1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5" t="s">
-        <v>7</v>
-      </c>
       <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="12" t="s">
+      <c r="K1" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="K1" s="12" t="s">
+      <c r="L1" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="L1" s="11" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="N1" s="11" t="s">
+      <c r="O1" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="O1" s="11" t="s">
+      <c r="P1" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="P1" s="11" t="s">
+      <c r="Q1" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="Q1" s="13" t="s">
-        <v>17</v>
-      </c>
       <c r="R1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="S1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="U1" s="10" t="s">
+      <c r="V1" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="V1" s="11" t="s">
+      <c r="W1" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="W1" s="9" t="s">
+      <c r="X1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Y1" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="Y1" s="9" t="s">
+      <c r="Z1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="AF1" s="1" t="s">
-        <v>34</v>
       </c>
       <c r="AG1" s="1"/>
       <c r="AH1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AI1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AI1" s="1" t="s">
+      <c r="AJ1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AJ1" s="1" t="s">
+      <c r="AK1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="AL1" s="1" t="s">
         <v>38</v>
-      </c>
-      <c r="AL1" s="1" t="s">
-        <v>39</v>
       </c>
       <c r="AM1" s="1"/>
       <c r="AN1" s="1"/>
@@ -763,34 +811,34 @@
     </row>
     <row r="2" spans="1:118" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="B2" s="4">
         <v>92</v>
       </c>
       <c r="C2" s="4">
-        <v>113</v>
+        <v>567</v>
       </c>
       <c r="D2" s="4">
         <v>2025</v>
       </c>
-      <c r="E2" s="10" t="s">
-        <v>19</v>
+      <c r="E2" s="9" t="s">
+        <v>18</v>
       </c>
       <c r="F2" s="6">
         <v>1</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H2" s="8">
+        <v>7</v>
+      </c>
+      <c r="H2" s="4">
         <v>2025</v>
       </c>
       <c r="I2" s="1">
         <v>19</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K2" s="1">
         <v>2025</v>
@@ -799,7 +847,7 @@
         <v>30</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N2" s="1">
         <v>2025</v>
@@ -808,7 +856,7 @@
         <v>15</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q2" s="1">
         <v>2025</v>
@@ -816,7 +864,7 @@
       <c r="R2" s="1"/>
       <c r="S2" s="1"/>
       <c r="T2" s="1"/>
-      <c r="U2" s="14"/>
+      <c r="U2" s="12"/>
       <c r="V2" s="1"/>
       <c r="W2" s="1"/>
       <c r="X2" s="1"/>
@@ -936,7 +984,7 @@
       <c r="R3" s="1"/>
       <c r="S3" s="1"/>
       <c r="T3" s="1"/>
-      <c r="U3" s="14"/>
+      <c r="U3" s="12"/>
       <c r="V3" s="1"/>
       <c r="W3" s="1"/>
       <c r="X3" s="1"/>
@@ -1056,7 +1104,7 @@
       <c r="R4" s="1"/>
       <c r="S4" s="1"/>
       <c r="T4" s="1"/>
-      <c r="U4" s="14"/>
+      <c r="U4" s="12"/>
       <c r="V4" s="1"/>
       <c r="W4" s="1"/>
       <c r="X4" s="1"/>
@@ -1176,7 +1224,7 @@
       <c r="R5" s="1"/>
       <c r="S5" s="1"/>
       <c r="T5" s="1"/>
-      <c r="U5" s="14"/>
+      <c r="U5" s="12"/>
       <c r="V5" s="1"/>
       <c r="W5" s="1"/>
       <c r="X5" s="1"/>
@@ -1476,4 +1524,127 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9177B227-E92D-4A4F-80A9-A49FCFC71FB6}">
+  <dimension ref="A1:K7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="E1" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="F1" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="G1" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="H1" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="I1" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="J1" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="K1" s="14" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" s="13"/>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="13"/>
+      <c r="K2" s="13"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="13"/>
+      <c r="B3" s="13"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="13"/>
+      <c r="I3" s="13"/>
+      <c r="J3" s="13"/>
+      <c r="K3" s="13"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="13"/>
+      <c r="B4" s="13"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="13"/>
+      <c r="J4" s="13"/>
+      <c r="K4" s="13"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="13"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="13"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="13"/>
+      <c r="G5" s="13"/>
+      <c r="H5" s="13"/>
+      <c r="I5" s="13"/>
+      <c r="J5" s="13"/>
+      <c r="K5" s="13"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" s="13"/>
+      <c r="B6" s="13"/>
+      <c r="C6" s="13"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="13"/>
+      <c r="J6" s="13"/>
+      <c r="K6" s="13"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" s="13"/>
+      <c r="B7" s="13"/>
+      <c r="C7" s="13"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="13"/>
+      <c r="F7" s="13"/>
+      <c r="G7" s="13"/>
+      <c r="H7" s="13"/>
+      <c r="I7" s="13"/>
+      <c r="J7" s="13"/>
+      <c r="K7" s="13"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Data/ON_Market.xlsx
+++ b/Data/ON_Market.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D19D67FC-3192-44D9-800A-6A49291FA31A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BB4A0E1-F5EF-4F55-B888-73E1DBC240DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11550" yWindow="105" windowWidth="8520" windowHeight="10605" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1755" yWindow="915" windowWidth="8520" windowHeight="10605" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settlement" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="53">
   <si>
     <t>ExchangeMaster</t>
   </si>
@@ -179,6 +179,12 @@
   </si>
   <si>
     <t>ENWR_No</t>
+  </si>
+  <si>
+    <t>Normal Payin</t>
+  </si>
+  <si>
+    <t>c10092043</t>
   </si>
 </sst>
 </file>
@@ -306,7 +312,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -322,6 +328,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1530,6 +1537,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9177B227-E92D-4A4F-80A9-A49FCFC71FB6}">
   <dimension ref="A1:K7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="6" max="6" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" customWidth="1"/>
+    <col min="11" max="11" width="18.42578125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="14" t="s">
@@ -1567,15 +1580,33 @@
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="13"/>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
-      <c r="I2" s="13"/>
+      <c r="A2" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="B2" s="13">
+        <v>6666101</v>
+      </c>
+      <c r="C2" s="13">
+        <v>9999996</v>
+      </c>
+      <c r="D2" s="13">
+        <v>1000421</v>
+      </c>
+      <c r="E2" s="13">
+        <v>15</v>
+      </c>
+      <c r="F2" s="15">
+        <v>100673000000011</v>
+      </c>
+      <c r="G2" s="13">
+        <v>973015</v>
+      </c>
+      <c r="H2" s="15">
+        <v>400920251740</v>
+      </c>
+      <c r="I2" s="15" t="s">
+        <v>52</v>
+      </c>
       <c r="J2" s="13"/>
       <c r="K2" s="13"/>
     </row>

--- a/Data/ON_Market.xlsx
+++ b/Data/ON_Market.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BB4A0E1-F5EF-4F55-B888-73E1DBC240DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AE43697-34EE-4510-8A45-11D65076C534}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1755" yWindow="915" windowWidth="8520" windowHeight="10605" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6705" yWindow="660" windowWidth="8520" windowHeight="10605" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settlement" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="55">
   <si>
     <t>ExchangeMaster</t>
   </si>
@@ -185,6 +185,12 @@
   </si>
   <si>
     <t>c10092043</t>
+  </si>
+  <si>
+    <t>Oct</t>
+  </si>
+  <si>
+    <t>Nov</t>
   </si>
 </sst>
 </file>
@@ -833,10 +839,10 @@
         <v>18</v>
       </c>
       <c r="F2" s="6">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>7</v>
+        <v>54</v>
       </c>
       <c r="H2" s="4">
         <v>2025</v>
@@ -845,7 +851,7 @@
         <v>19</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>7</v>
+        <v>53</v>
       </c>
       <c r="K2" s="1">
         <v>2025</v>
@@ -1538,6 +1544,7 @@
   <dimension ref="A1:K7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="1" width="15.5703125" customWidth="1"/>
     <col min="6" max="6" width="16.140625" bestFit="1" customWidth="1"/>
     <col min="8" max="9" width="16.140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="15.7109375" customWidth="1"/>
@@ -1607,20 +1614,42 @@
       <c r="I2" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="J2" s="13"/>
+      <c r="J2" s="13">
+        <v>11922025567</v>
+      </c>
       <c r="K2" s="13"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="13"/>
-      <c r="B3" s="13"/>
-      <c r="C3" s="13"/>
-      <c r="D3" s="13"/>
-      <c r="E3" s="13"/>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13"/>
-      <c r="H3" s="13"/>
-      <c r="I3" s="13"/>
-      <c r="J3" s="13"/>
+      <c r="A3" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="B3" s="13">
+        <v>6666101</v>
+      </c>
+      <c r="C3" s="13">
+        <v>9996059</v>
+      </c>
+      <c r="D3" s="13">
+        <v>5750013</v>
+      </c>
+      <c r="E3" s="13">
+        <v>1</v>
+      </c>
+      <c r="F3" s="15">
+        <v>100673000000011</v>
+      </c>
+      <c r="G3" s="13">
+        <v>973015</v>
+      </c>
+      <c r="H3" s="15">
+        <v>400920251740</v>
+      </c>
+      <c r="I3" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="J3" s="13">
+        <v>11922025909</v>
+      </c>
       <c r="K3" s="13"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">

--- a/Data/ON_Market.xlsx
+++ b/Data/ON_Market.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AE43697-34EE-4510-8A45-11D65076C534}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0100D30-9851-48C1-8712-058F539289F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6705" yWindow="660" windowWidth="8520" windowHeight="10605" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settlement" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="58">
   <si>
     <t>ExchangeMaster</t>
   </si>
@@ -191,13 +191,22 @@
   </si>
   <si>
     <t>Nov</t>
+  </si>
+  <si>
+    <t>no_of_bags</t>
+  </si>
+  <si>
+    <t>Early Payin</t>
+  </si>
+  <si>
+    <t>deliveryunit</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -257,8 +266,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -274,6 +290,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -318,7 +340,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -335,6 +357,8 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1541,7 +1565,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9177B227-E92D-4A4F-80A9-A49FCFC71FB6}">
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.5703125" customWidth="1"/>
@@ -1549,9 +1573,10 @@
     <col min="8" max="9" width="16.140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="15.7109375" customWidth="1"/>
     <col min="11" max="11" width="18.42578125" customWidth="1"/>
+    <col min="13" max="13" width="13.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="14" t="s">
         <v>40</v>
       </c>
@@ -1585,8 +1610,14 @@
       <c r="K1" s="14" t="s">
         <v>50</v>
       </c>
+      <c r="L1" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M1" s="17" t="s">
+        <v>57</v>
+      </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
         <v>51</v>
       </c>
@@ -1617,14 +1648,18 @@
       <c r="J2" s="13">
         <v>11922025567</v>
       </c>
-      <c r="K2" s="13"/>
+      <c r="K2" s="15">
+        <v>110001017786</v>
+      </c>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
         <v>51</v>
       </c>
       <c r="B3" s="13">
-        <v>6666101</v>
+        <v>6666102</v>
       </c>
       <c r="C3" s="13">
         <v>9996059</v>
@@ -1633,7 +1668,7 @@
         <v>5750013</v>
       </c>
       <c r="E3" s="13">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="F3" s="15">
         <v>100673000000011</v>
@@ -1648,24 +1683,58 @@
         <v>52</v>
       </c>
       <c r="J3" s="13">
+        <v>11922025567</v>
+      </c>
+      <c r="K3" s="15">
+        <v>110001017802</v>
+      </c>
+      <c r="L3" s="15">
+        <v>200</v>
+      </c>
+      <c r="M3" s="1"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="B4" s="13">
+        <v>6666103</v>
+      </c>
+      <c r="C4" s="13">
+        <v>9999996</v>
+      </c>
+      <c r="D4" s="13">
+        <v>1000421</v>
+      </c>
+      <c r="E4" s="13">
+        <v>1</v>
+      </c>
+      <c r="F4" s="15">
+        <v>100673000000011</v>
+      </c>
+      <c r="G4" s="13">
+        <v>973015</v>
+      </c>
+      <c r="H4" s="15">
+        <v>400920251740</v>
+      </c>
+      <c r="I4" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="J4" s="13">
         <v>11922025909</v>
       </c>
-      <c r="K3" s="13"/>
+      <c r="K4" s="15">
+        <v>110001023792</v>
+      </c>
+      <c r="L4" s="1">
+        <v>100</v>
+      </c>
+      <c r="M4" s="15">
+        <v>1</v>
+      </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="13"/>
-      <c r="B4" s="13"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="13"/>
-      <c r="H4" s="13"/>
-      <c r="I4" s="13"/>
-      <c r="J4" s="13"/>
-      <c r="K4" s="13"/>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="13"/>
       <c r="B5" s="13"/>
       <c r="C5" s="13"/>
@@ -1675,10 +1744,16 @@
       <c r="G5" s="13"/>
       <c r="H5" s="13"/>
       <c r="I5" s="13"/>
-      <c r="J5" s="13"/>
+      <c r="J5" s="13">
+        <v>11922025567</v>
+      </c>
       <c r="K5" s="13"/>
+      <c r="L5" s="1">
+        <v>1</v>
+      </c>
+      <c r="M5" s="1"/>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="13"/>
       <c r="B6" s="13"/>
       <c r="C6" s="13"/>
@@ -1688,10 +1763,14 @@
       <c r="G6" s="13"/>
       <c r="H6" s="13"/>
       <c r="I6" s="13"/>
-      <c r="J6" s="13"/>
+      <c r="J6" s="13">
+        <v>11922025909</v>
+      </c>
       <c r="K6" s="13"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="13"/>
       <c r="B7" s="13"/>
       <c r="C7" s="13"/>
@@ -1703,6 +1782,8 @@
       <c r="I7" s="13"/>
       <c r="J7" s="13"/>
       <c r="K7" s="13"/>
+      <c r="L7" s="1"/>
+      <c r="M7" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Data/ON_Market.xlsx
+++ b/Data/ON_Market.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0100D30-9851-48C1-8712-058F539289F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6D4E13A-1E0D-4B90-8100-457B8C7AA81B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settlement" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="57">
   <si>
     <t>ExchangeMaster</t>
   </si>
@@ -47,9 +47,6 @@
   </si>
   <si>
     <t>expectedYear</t>
-  </si>
-  <si>
-    <t>October</t>
   </si>
   <si>
     <t>trade_Day</t>
@@ -206,7 +203,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -248,13 +245,6 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="Consolas"/>
-      <family val="3"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
       <name val="Consolas"/>
       <family val="3"/>
     </font>
@@ -349,16 +339,16 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -650,6 +640,32 @@
     <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="17.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
+    <col min="12" max="14" width="25.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="20.85546875" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="24" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:118" x14ac:dyDescent="0.25">
@@ -666,7 +682,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F1" s="5" t="s">
         <v>4</v>
@@ -678,78 +694,80 @@
         <v>6</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="11" t="s">
+      <c r="K1" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="11" t="s">
+      <c r="L1" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="10" t="s">
+      <c r="M1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="10" t="s">
+      <c r="O1" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="10" t="s">
+      <c r="P1" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="10" t="s">
+      <c r="Q1" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="10" t="s">
-        <v>16</v>
-      </c>
       <c r="R1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="S1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="U1" s="9" t="s">
+      <c r="V1" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="V1" s="10" t="s">
+      <c r="W1" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="W1" s="8" t="s">
+      <c r="X1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Y1" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="Y1" s="8" t="s">
+      <c r="Z1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AG1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="AG1" s="1"/>
       <c r="AH1" s="1" t="s">
         <v>34</v>
       </c>
@@ -762,9 +780,7 @@
       <c r="AK1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AL1" s="1" t="s">
-        <v>38</v>
-      </c>
+      <c r="AL1" s="1"/>
       <c r="AM1" s="1"/>
       <c r="AN1" s="1"/>
       <c r="AO1" s="1"/>
@@ -848,7 +864,7 @@
     </row>
     <row r="2" spans="1:118" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B2" s="4">
         <v>92</v>
@@ -859,32 +875,32 @@
       <c r="D2" s="4">
         <v>2025</v>
       </c>
-      <c r="E2" s="9" t="s">
-        <v>18</v>
+      <c r="E2" s="8" t="s">
+        <v>17</v>
       </c>
       <c r="F2" s="6">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H2" s="4">
         <v>2025</v>
       </c>
       <c r="I2" s="1">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K2" s="1">
         <v>2025</v>
       </c>
       <c r="L2" s="1">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>7</v>
+        <v>53</v>
       </c>
       <c r="N2" s="1">
         <v>2025</v>
@@ -893,7 +909,7 @@
         <v>15</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>7</v>
+        <v>52</v>
       </c>
       <c r="Q2" s="1">
         <v>2025</v>
@@ -901,7 +917,7 @@
       <c r="R2" s="1"/>
       <c r="S2" s="1"/>
       <c r="T2" s="1"/>
-      <c r="U2" s="12"/>
+      <c r="U2" s="11"/>
       <c r="V2" s="1"/>
       <c r="W2" s="1"/>
       <c r="X2" s="1"/>
@@ -1021,7 +1037,7 @@
       <c r="R3" s="1"/>
       <c r="S3" s="1"/>
       <c r="T3" s="1"/>
-      <c r="U3" s="12"/>
+      <c r="U3" s="11"/>
       <c r="V3" s="1"/>
       <c r="W3" s="1"/>
       <c r="X3" s="1"/>
@@ -1141,7 +1157,7 @@
       <c r="R4" s="1"/>
       <c r="S4" s="1"/>
       <c r="T4" s="1"/>
-      <c r="U4" s="12"/>
+      <c r="U4" s="11"/>
       <c r="V4" s="1"/>
       <c r="W4" s="1"/>
       <c r="X4" s="1"/>
@@ -1261,7 +1277,7 @@
       <c r="R5" s="1"/>
       <c r="S5" s="1"/>
       <c r="T5" s="1"/>
-      <c r="U5" s="12"/>
+      <c r="U5" s="11"/>
       <c r="V5" s="1"/>
       <c r="W5" s="1"/>
       <c r="X5" s="1"/>
@@ -1577,211 +1593,211 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="B1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="C1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="D1" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="E1" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="F1" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="G1" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="H1" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="I1" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="I1" s="14" t="s">
+      <c r="J1" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="J1" s="14" t="s">
+      <c r="K1" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="K1" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="L1" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="M1" s="17" t="s">
-        <v>57</v>
+      <c r="L1" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="M1" s="16" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="B2" s="12">
+        <v>6666101</v>
+      </c>
+      <c r="C2" s="12">
+        <v>9999996</v>
+      </c>
+      <c r="D2" s="12">
+        <v>1000421</v>
+      </c>
+      <c r="E2" s="12">
+        <v>15</v>
+      </c>
+      <c r="F2" s="14">
+        <v>100673000000011</v>
+      </c>
+      <c r="G2" s="12">
+        <v>973015</v>
+      </c>
+      <c r="H2" s="14">
+        <v>400920251740</v>
+      </c>
+      <c r="I2" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="B2" s="13">
-        <v>6666101</v>
-      </c>
-      <c r="C2" s="13">
-        <v>9999996</v>
-      </c>
-      <c r="D2" s="13">
-        <v>1000421</v>
-      </c>
-      <c r="E2" s="13">
-        <v>15</v>
-      </c>
-      <c r="F2" s="15">
-        <v>100673000000011</v>
-      </c>
-      <c r="G2" s="13">
-        <v>973015</v>
-      </c>
-      <c r="H2" s="15">
-        <v>400920251740</v>
-      </c>
-      <c r="I2" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="J2" s="13">
+      <c r="J2" s="12">
         <v>11922025567</v>
       </c>
-      <c r="K2" s="15">
+      <c r="K2" s="14">
         <v>110001017786</v>
       </c>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="B3" s="12">
+        <v>6666102</v>
+      </c>
+      <c r="C3" s="12">
+        <v>9996059</v>
+      </c>
+      <c r="D3" s="12">
+        <v>5750013</v>
+      </c>
+      <c r="E3" s="12">
+        <v>15</v>
+      </c>
+      <c r="F3" s="14">
+        <v>100673000000011</v>
+      </c>
+      <c r="G3" s="12">
+        <v>973015</v>
+      </c>
+      <c r="H3" s="14">
+        <v>400920251740</v>
+      </c>
+      <c r="I3" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="B3" s="13">
-        <v>6666102</v>
-      </c>
-      <c r="C3" s="13">
-        <v>9996059</v>
-      </c>
-      <c r="D3" s="13">
-        <v>5750013</v>
-      </c>
-      <c r="E3" s="13">
-        <v>15</v>
-      </c>
-      <c r="F3" s="15">
-        <v>100673000000011</v>
-      </c>
-      <c r="G3" s="13">
-        <v>973015</v>
-      </c>
-      <c r="H3" s="15">
-        <v>400920251740</v>
-      </c>
-      <c r="I3" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="J3" s="13">
+      <c r="J3" s="12">
         <v>11922025567</v>
       </c>
-      <c r="K3" s="15">
+      <c r="K3" s="14">
         <v>110001017802</v>
       </c>
-      <c r="L3" s="15">
+      <c r="L3" s="14">
         <v>200</v>
       </c>
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="B4" s="13">
+      <c r="A4" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="B4" s="12">
         <v>6666103</v>
       </c>
-      <c r="C4" s="13">
+      <c r="C4" s="12">
         <v>9999996</v>
       </c>
-      <c r="D4" s="13">
+      <c r="D4" s="12">
         <v>1000421</v>
       </c>
-      <c r="E4" s="13">
+      <c r="E4" s="12">
         <v>1</v>
       </c>
-      <c r="F4" s="15">
+      <c r="F4" s="14">
         <v>100673000000011</v>
       </c>
-      <c r="G4" s="13">
+      <c r="G4" s="12">
         <v>973015</v>
       </c>
-      <c r="H4" s="15">
+      <c r="H4" s="14">
         <v>400920251740</v>
       </c>
-      <c r="I4" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="J4" s="13">
+      <c r="I4" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="J4" s="12">
         <v>11922025909</v>
       </c>
-      <c r="K4" s="15">
+      <c r="K4" s="14">
         <v>110001023792</v>
       </c>
       <c r="L4" s="1">
         <v>100</v>
       </c>
-      <c r="M4" s="15">
+      <c r="M4" s="14">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A5" s="13"/>
-      <c r="B5" s="13"/>
-      <c r="C5" s="13"/>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="13"/>
-      <c r="G5" s="13"/>
-      <c r="H5" s="13"/>
-      <c r="I5" s="13"/>
-      <c r="J5" s="13">
+      <c r="A5" s="12"/>
+      <c r="B5" s="12"/>
+      <c r="C5" s="12"/>
+      <c r="D5" s="12"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="12"/>
+      <c r="H5" s="12"/>
+      <c r="I5" s="12"/>
+      <c r="J5" s="12">
         <v>11922025567</v>
       </c>
-      <c r="K5" s="13"/>
+      <c r="K5" s="12"/>
       <c r="L5" s="1">
         <v>1</v>
       </c>
       <c r="M5" s="1"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A6" s="13"/>
-      <c r="B6" s="13"/>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
-      <c r="I6" s="13"/>
-      <c r="J6" s="13">
+      <c r="A6" s="12"/>
+      <c r="B6" s="12"/>
+      <c r="C6" s="12"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="12"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="12">
         <v>11922025909</v>
       </c>
-      <c r="K6" s="13"/>
+      <c r="K6" s="12"/>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A7" s="13"/>
-      <c r="B7" s="13"/>
-      <c r="C7" s="13"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13"/>
-      <c r="H7" s="13"/>
-      <c r="I7" s="13"/>
-      <c r="J7" s="13"/>
-      <c r="K7" s="13"/>
+      <c r="A7" s="12"/>
+      <c r="B7" s="12"/>
+      <c r="C7" s="12"/>
+      <c r="D7" s="12"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="12"/>
+      <c r="H7" s="12"/>
+      <c r="I7" s="12"/>
+      <c r="J7" s="12"/>
+      <c r="K7" s="12"/>
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
     </row>

--- a/Data/ON_Market.xlsx
+++ b/Data/ON_Market.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6D4E13A-1E0D-4B90-8100-457B8C7AA81B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A1EB01D-C4C6-4CA9-8316-F26DC2562E41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4935" yWindow="300" windowWidth="8520" windowHeight="10605" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settlement" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="39">
   <si>
     <t>ExchangeMaster</t>
   </si>
@@ -43,39 +43,9 @@
     <t>expectedDay</t>
   </si>
   <si>
-    <t>expectedMonth</t>
-  </si>
-  <si>
-    <t>expectedYear</t>
-  </si>
-  <si>
     <t>trade_Day</t>
   </si>
   <si>
-    <t>trade_Month</t>
-  </si>
-  <si>
-    <t>trade_Year</t>
-  </si>
-  <si>
-    <t>PostExpiry_Validity_Date</t>
-  </si>
-  <si>
-    <t>PostExpiry_Validity_Month</t>
-  </si>
-  <si>
-    <t>PostExpiry_Validity_Year</t>
-  </si>
-  <si>
-    <t>Delivery_Marking</t>
-  </si>
-  <si>
-    <t>Delivery_Marking_Month</t>
-  </si>
-  <si>
-    <t>Delivery_Marking_Year</t>
-  </si>
-  <si>
     <t>commodity</t>
   </si>
   <si>
@@ -85,12 +55,6 @@
     <t>pay_In_date</t>
   </si>
   <si>
-    <t>pay_In_Month</t>
-  </si>
-  <si>
-    <t>pay_In_Year</t>
-  </si>
-  <si>
     <t>pay_In_Date_hr</t>
   </si>
   <si>
@@ -100,12 +64,6 @@
     <t>pay_out_date</t>
   </si>
   <si>
-    <t>pay_out_Month</t>
-  </si>
-  <si>
-    <t>pay_out_Year</t>
-  </si>
-  <si>
     <t>pay_out_Date_hr</t>
   </si>
   <si>
@@ -115,12 +73,6 @@
     <t>early_pay_In_date</t>
   </si>
   <si>
-    <t>early_pay_In_Month</t>
-  </si>
-  <si>
-    <t>early_pay_In_Year</t>
-  </si>
-  <si>
     <t>early_pay_In_Date_hr</t>
   </si>
   <si>
@@ -130,12 +82,6 @@
     <t>early_Payin_End_date</t>
   </si>
   <si>
-    <t>early_Payin_End_Month</t>
-  </si>
-  <si>
-    <t>early_Payin_End_Year</t>
-  </si>
-  <si>
     <t>early_Payin_End_Date_hr</t>
   </si>
   <si>
@@ -184,12 +130,6 @@
     <t>c10092043</t>
   </si>
   <si>
-    <t>Oct</t>
-  </si>
-  <si>
-    <t>Nov</t>
-  </si>
-  <si>
     <t>no_of_bags</t>
   </si>
   <si>
@@ -197,13 +137,22 @@
   </si>
   <si>
     <t>deliveryunit</t>
+  </si>
+  <si>
+    <t>PostExpiry_Validity_Day</t>
+  </si>
+  <si>
+    <t>Delivery_Marking_Day</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="[$-14009]dd/mm/yyyy;@"/>
+  </numFmts>
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -262,6 +211,12 @@
       <color rgb="FF000000"/>
       <name val="Consolas"/>
       <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF2A314A"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="5">
@@ -330,18 +285,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -349,6 +300,11 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -636,21 +592,24 @@
     <col min="2" max="2" width="16.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.140625" customWidth="1"/>
+    <col min="5" max="5" width="18.28515625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.42578125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="12" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
-    <col min="12" max="14" width="25.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.85546875" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" customWidth="1"/>
+    <col min="14" max="14" width="25.5703125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="17.28515625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="23.42578125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="22.42578125" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="20.85546875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="24" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="15.140625" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="13.140625" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="15.140625" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="13.140625" bestFit="1" customWidth="1"/>
@@ -682,104 +641,72 @@
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="I1" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="J1" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="P1" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q1" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="R1" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="F1" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="L1" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="N1" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="O1" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="P1" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q1" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="T1" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="U1" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="T1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="U1" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="V1" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="W1" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="Y1" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="AC1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="AD1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="AE1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="AF1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="AG1" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="AH1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="AI1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="AJ1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AK1" s="1" t="s">
-        <v>37</v>
-      </c>
+      <c r="V1" s="6"/>
+      <c r="W1" s="13"/>
+      <c r="X1" s="1"/>
+      <c r="Y1" s="13"/>
+      <c r="Z1" s="1"/>
+      <c r="AA1" s="1"/>
+      <c r="AB1" s="1"/>
+      <c r="AC1" s="1"/>
+      <c r="AD1" s="1"/>
+      <c r="AE1" s="1"/>
+      <c r="AF1" s="1"/>
+      <c r="AG1" s="1"/>
+      <c r="AH1" s="1"/>
+      <c r="AI1" s="1"/>
+      <c r="AJ1" s="1"/>
+      <c r="AK1" s="1"/>
       <c r="AL1" s="1"/>
       <c r="AM1" s="1"/>
       <c r="AN1" s="1"/>
@@ -864,60 +791,68 @@
     </row>
     <row r="2" spans="1:118" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="B2" s="4">
         <v>92</v>
       </c>
-      <c r="C2" s="4">
-        <v>567</v>
+      <c r="C2" s="18">
+        <v>160</v>
       </c>
       <c r="D2" s="4">
         <v>2025</v>
       </c>
-      <c r="E2" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="F2" s="6">
-        <v>13</v>
-      </c>
-      <c r="G2" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="H2" s="4">
-        <v>2025</v>
-      </c>
-      <c r="I2" s="1">
-        <v>17</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>52</v>
+      <c r="E2" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" s="15">
+        <v>45961</v>
+      </c>
+      <c r="G2" s="5">
+        <v>45939</v>
+      </c>
+      <c r="H2" s="15">
+        <v>45961</v>
+      </c>
+      <c r="I2" s="5">
+        <v>45939</v>
+      </c>
+      <c r="J2" s="15">
+        <v>45961</v>
       </c>
       <c r="K2" s="1">
-        <v>2025</v>
+        <v>4</v>
       </c>
       <c r="L2" s="1">
-        <v>9</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>53</v>
+        <v>4</v>
+      </c>
+      <c r="M2" s="15">
+        <v>45961</v>
       </c>
       <c r="N2" s="1">
-        <v>2025</v>
+        <v>6</v>
       </c>
       <c r="O2" s="1">
-        <v>15</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>52</v>
+        <v>5</v>
+      </c>
+      <c r="P2" s="16">
+        <v>45955</v>
       </c>
       <c r="Q2" s="1">
-        <v>2025</v>
-      </c>
-      <c r="R2" s="1"/>
-      <c r="S2" s="1"/>
-      <c r="T2" s="1"/>
-      <c r="U2" s="11"/>
+        <v>6</v>
+      </c>
+      <c r="R2" s="1">
+        <v>6</v>
+      </c>
+      <c r="S2" s="16">
+        <v>45955</v>
+      </c>
+      <c r="T2" s="1">
+        <v>7</v>
+      </c>
+      <c r="U2" s="7">
+        <v>7</v>
+      </c>
       <c r="V2" s="1"/>
       <c r="W2" s="1"/>
       <c r="X2" s="1"/>
@@ -1037,7 +972,7 @@
       <c r="R3" s="1"/>
       <c r="S3" s="1"/>
       <c r="T3" s="1"/>
-      <c r="U3" s="11"/>
+      <c r="U3" s="7"/>
       <c r="V3" s="1"/>
       <c r="W3" s="1"/>
       <c r="X3" s="1"/>
@@ -1157,7 +1092,7 @@
       <c r="R4" s="1"/>
       <c r="S4" s="1"/>
       <c r="T4" s="1"/>
-      <c r="U4" s="11"/>
+      <c r="U4" s="7"/>
       <c r="V4" s="1"/>
       <c r="W4" s="1"/>
       <c r="X4" s="1"/>
@@ -1277,7 +1212,7 @@
       <c r="R5" s="1"/>
       <c r="S5" s="1"/>
       <c r="T5" s="1"/>
-      <c r="U5" s="11"/>
+      <c r="U5" s="7"/>
       <c r="V5" s="1"/>
       <c r="W5" s="1"/>
       <c r="X5" s="1"/>
@@ -1581,7 +1516,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9177B227-E92D-4A4F-80A9-A49FCFC71FB6}">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.5703125" customWidth="1"/>
@@ -1593,213 +1528,220 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="B1" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="C1" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="D1" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="E1" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="F1" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="G1" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="H1" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="I1" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="J1" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="K1" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="L1" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="M1" s="16" t="s">
-        <v>56</v>
+      <c r="A1" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="K1" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L1" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="M1" s="12" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="B2" s="12">
+      <c r="A2" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="B2" s="8">
         <v>6666101</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="8">
         <v>9999996</v>
       </c>
-      <c r="D2" s="12">
+      <c r="D2" s="8">
         <v>1000421</v>
       </c>
-      <c r="E2" s="12">
+      <c r="E2" s="8">
         <v>15</v>
       </c>
-      <c r="F2" s="14">
+      <c r="F2" s="10">
         <v>100673000000011</v>
       </c>
-      <c r="G2" s="12">
+      <c r="G2" s="8">
         <v>973015</v>
       </c>
-      <c r="H2" s="14">
+      <c r="H2" s="10">
         <v>400920251740</v>
       </c>
-      <c r="I2" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="J2" s="12">
+      <c r="I2" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="J2" s="8">
         <v>11922025567</v>
       </c>
-      <c r="K2" s="14">
+      <c r="K2" s="10">
         <v>110001017786</v>
       </c>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A3" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="B3" s="12">
+      <c r="A3" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" s="8">
         <v>6666102</v>
       </c>
-      <c r="C3" s="12">
+      <c r="C3" s="8">
         <v>9996059</v>
       </c>
-      <c r="D3" s="12">
+      <c r="D3" s="8">
         <v>5750013</v>
       </c>
-      <c r="E3" s="12">
+      <c r="E3" s="8">
         <v>15</v>
       </c>
-      <c r="F3" s="14">
+      <c r="F3" s="10">
         <v>100673000000011</v>
       </c>
-      <c r="G3" s="12">
+      <c r="G3" s="8">
         <v>973015</v>
       </c>
-      <c r="H3" s="14">
+      <c r="H3" s="10">
         <v>400920251740</v>
       </c>
-      <c r="I3" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="J3" s="12">
-        <v>11922025567</v>
-      </c>
-      <c r="K3" s="14">
-        <v>110001017802</v>
-      </c>
-      <c r="L3" s="14">
-        <v>200</v>
+      <c r="I3" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="J3" s="8">
+        <v>11922025160</v>
+      </c>
+      <c r="K3" s="10">
+        <v>110001017943</v>
+      </c>
+      <c r="L3" s="10">
+        <v>100</v>
       </c>
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="B4" s="12">
+      <c r="A4" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" s="8">
         <v>6666103</v>
       </c>
-      <c r="C4" s="12">
+      <c r="C4" s="8">
         <v>9999996</v>
       </c>
-      <c r="D4" s="12">
+      <c r="D4" s="8">
         <v>1000421</v>
       </c>
-      <c r="E4" s="12">
+      <c r="E4" s="8">
         <v>1</v>
       </c>
-      <c r="F4" s="14">
+      <c r="F4" s="10">
         <v>100673000000011</v>
       </c>
-      <c r="G4" s="12">
+      <c r="G4" s="8">
         <v>973015</v>
       </c>
-      <c r="H4" s="14">
+      <c r="H4" s="10">
         <v>400920251740</v>
       </c>
-      <c r="I4" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="J4" s="12">
+      <c r="I4" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="J4" s="8">
         <v>11922025909</v>
       </c>
-      <c r="K4" s="14">
+      <c r="K4" s="10">
         <v>110001023792</v>
       </c>
       <c r="L4" s="1">
         <v>100</v>
       </c>
-      <c r="M4" s="14">
+      <c r="M4" s="10">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A5" s="12"/>
-      <c r="B5" s="12"/>
-      <c r="C5" s="12"/>
-      <c r="D5" s="12"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="12"/>
-      <c r="H5" s="12"/>
-      <c r="I5" s="12"/>
-      <c r="J5" s="12">
+      <c r="A5" s="8"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="8">
         <v>11922025567</v>
       </c>
-      <c r="K5" s="12"/>
+      <c r="K5" s="8"/>
       <c r="L5" s="1">
         <v>1</v>
       </c>
       <c r="M5" s="1"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A6" s="12"/>
-      <c r="B6" s="12"/>
-      <c r="C6" s="12"/>
-      <c r="D6" s="12"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="12"/>
-      <c r="J6" s="12">
+      <c r="A6" s="8"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="8"/>
+      <c r="J6" s="8">
         <v>11922025909</v>
       </c>
-      <c r="K6" s="12"/>
+      <c r="K6" s="8"/>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A7" s="12"/>
-      <c r="B7" s="12"/>
-      <c r="C7" s="12"/>
-      <c r="D7" s="12"/>
-      <c r="E7" s="12"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="12"/>
-      <c r="H7" s="12"/>
-      <c r="I7" s="12"/>
-      <c r="J7" s="12"/>
-      <c r="K7" s="12"/>
+      <c r="A7" s="8"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="17">
+        <v>11922025908</v>
+      </c>
+      <c r="K7" s="8"/>
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="J8" s="8">
+        <v>11922025999</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Data/ON_Market.xlsx
+++ b/Data/ON_Market.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A1EB01D-C4C6-4CA9-8316-F26DC2562E41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F723633-3DFB-46D0-AEA1-B5692C518605}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4935" yWindow="300" windowWidth="8520" windowHeight="10605" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settlement" sheetId="1" r:id="rId1"/>
@@ -150,7 +150,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="[$-14009]dd/mm/yyyy;@"/>
+    <numFmt numFmtId="167" formatCode="dd\/mm\/yyyy"/>
   </numFmts>
   <fonts count="10" x14ac:knownFonts="1">
     <font>
@@ -285,13 +285,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -301,10 +300,9 @@
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -643,58 +641,58 @@
       <c r="E1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="H1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="I1" s="14" t="s">
+      <c r="I1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="J1" s="14" t="s">
+      <c r="J1" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="14" t="s">
+      <c r="K1" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="14" t="s">
+      <c r="L1" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="14" t="s">
+      <c r="M1" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="14" t="s">
+      <c r="N1" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="14" t="s">
+      <c r="O1" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="14" t="s">
+      <c r="P1" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="14" t="s">
+      <c r="Q1" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="R1" s="14" t="s">
+      <c r="R1" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="S1" s="9" t="s">
+      <c r="S1" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="T1" s="9" t="s">
+      <c r="T1" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="U1" s="14" t="s">
+      <c r="U1" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="V1" s="6"/>
-      <c r="W1" s="13"/>
+      <c r="V1" s="5"/>
+      <c r="W1" s="12"/>
       <c r="X1" s="1"/>
-      <c r="Y1" s="13"/>
+      <c r="Y1" s="12"/>
       <c r="Z1" s="1"/>
       <c r="AA1" s="1"/>
       <c r="AB1" s="1"/>
@@ -796,28 +794,28 @@
       <c r="B2" s="4">
         <v>92</v>
       </c>
-      <c r="C2" s="18">
+      <c r="C2" s="4">
         <v>160</v>
       </c>
       <c r="D2" s="4">
         <v>2025</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="15">
+      <c r="F2" s="16">
         <v>45961</v>
       </c>
-      <c r="G2" s="5">
+      <c r="G2" s="15">
         <v>45939</v>
       </c>
-      <c r="H2" s="15">
+      <c r="H2" s="16">
         <v>45961</v>
       </c>
-      <c r="I2" s="5">
+      <c r="I2" s="15">
         <v>45939</v>
       </c>
-      <c r="J2" s="15">
+      <c r="J2" s="16">
         <v>45961</v>
       </c>
       <c r="K2" s="1">
@@ -826,7 +824,7 @@
       <c r="L2" s="1">
         <v>4</v>
       </c>
-      <c r="M2" s="15">
+      <c r="M2" s="16">
         <v>45961</v>
       </c>
       <c r="N2" s="1">
@@ -850,7 +848,7 @@
       <c r="T2" s="1">
         <v>7</v>
       </c>
-      <c r="U2" s="7">
+      <c r="U2" s="6">
         <v>7</v>
       </c>
       <c r="V2" s="1"/>
@@ -972,7 +970,7 @@
       <c r="R3" s="1"/>
       <c r="S3" s="1"/>
       <c r="T3" s="1"/>
-      <c r="U3" s="7"/>
+      <c r="U3" s="6"/>
       <c r="V3" s="1"/>
       <c r="W3" s="1"/>
       <c r="X3" s="1"/>
@@ -1092,7 +1090,7 @@
       <c r="R4" s="1"/>
       <c r="S4" s="1"/>
       <c r="T4" s="1"/>
-      <c r="U4" s="7"/>
+      <c r="U4" s="6"/>
       <c r="V4" s="1"/>
       <c r="W4" s="1"/>
       <c r="X4" s="1"/>
@@ -1212,7 +1210,7 @@
       <c r="R5" s="1"/>
       <c r="S5" s="1"/>
       <c r="T5" s="1"/>
-      <c r="U5" s="7"/>
+      <c r="U5" s="6"/>
       <c r="V5" s="1"/>
       <c r="W5" s="1"/>
       <c r="X5" s="1"/>
@@ -1528,218 +1526,218 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I1" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="J1" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="K1" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="L1" s="11" t="s">
+      <c r="L1" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="M1" s="12" t="s">
+      <c r="M1" s="11" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="B2" s="8">
+      <c r="B2" s="7">
         <v>6666101</v>
       </c>
-      <c r="C2" s="8">
+      <c r="C2" s="7">
         <v>9999996</v>
       </c>
-      <c r="D2" s="8">
+      <c r="D2" s="7">
         <v>1000421</v>
       </c>
-      <c r="E2" s="8">
+      <c r="E2" s="7">
         <v>15</v>
       </c>
-      <c r="F2" s="10">
+      <c r="F2" s="9">
         <v>100673000000011</v>
       </c>
-      <c r="G2" s="8">
+      <c r="G2" s="7">
         <v>973015</v>
       </c>
-      <c r="H2" s="10">
+      <c r="H2" s="9">
         <v>400920251740</v>
       </c>
-      <c r="I2" s="10" t="s">
+      <c r="I2" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="J2" s="8">
+      <c r="J2" s="7">
         <v>11922025567</v>
       </c>
-      <c r="K2" s="10">
+      <c r="K2" s="9">
         <v>110001017786</v>
       </c>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="8">
+      <c r="B3" s="7">
         <v>6666102</v>
       </c>
-      <c r="C3" s="8">
+      <c r="C3" s="7">
         <v>9996059</v>
       </c>
-      <c r="D3" s="8">
+      <c r="D3" s="7">
         <v>5750013</v>
       </c>
-      <c r="E3" s="8">
+      <c r="E3" s="7">
         <v>15</v>
       </c>
-      <c r="F3" s="10">
+      <c r="F3" s="9">
         <v>100673000000011</v>
       </c>
-      <c r="G3" s="8">
+      <c r="G3" s="7">
         <v>973015</v>
       </c>
-      <c r="H3" s="10">
+      <c r="H3" s="9">
         <v>400920251740</v>
       </c>
-      <c r="I3" s="10" t="s">
+      <c r="I3" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="J3" s="8">
+      <c r="J3" s="7">
         <v>11922025160</v>
       </c>
-      <c r="K3" s="10">
+      <c r="K3" s="9">
         <v>110001017943</v>
       </c>
-      <c r="L3" s="10">
+      <c r="L3" s="9">
         <v>100</v>
       </c>
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="B4" s="8">
+      <c r="B4" s="7">
         <v>6666103</v>
       </c>
-      <c r="C4" s="8">
+      <c r="C4" s="7">
         <v>9999996</v>
       </c>
-      <c r="D4" s="8">
+      <c r="D4" s="7">
         <v>1000421</v>
       </c>
-      <c r="E4" s="8">
+      <c r="E4" s="7">
         <v>1</v>
       </c>
-      <c r="F4" s="10">
+      <c r="F4" s="9">
         <v>100673000000011</v>
       </c>
-      <c r="G4" s="8">
+      <c r="G4" s="7">
         <v>973015</v>
       </c>
-      <c r="H4" s="10">
+      <c r="H4" s="9">
         <v>400920251740</v>
       </c>
-      <c r="I4" s="10" t="s">
+      <c r="I4" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="J4" s="8">
+      <c r="J4" s="7">
         <v>11922025909</v>
       </c>
-      <c r="K4" s="10">
+      <c r="K4" s="9">
         <v>110001023792</v>
       </c>
       <c r="L4" s="1">
         <v>100</v>
       </c>
-      <c r="M4" s="10">
+      <c r="M4" s="9">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A5" s="8"/>
-      <c r="B5" s="8"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
-      <c r="H5" s="8"/>
-      <c r="I5" s="8"/>
-      <c r="J5" s="8">
+      <c r="A5" s="7"/>
+      <c r="B5" s="7"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7"/>
+      <c r="I5" s="7"/>
+      <c r="J5" s="7">
         <v>11922025567</v>
       </c>
-      <c r="K5" s="8"/>
+      <c r="K5" s="7"/>
       <c r="L5" s="1">
         <v>1</v>
       </c>
       <c r="M5" s="1"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A6" s="8"/>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
-      <c r="I6" s="8"/>
-      <c r="J6" s="8">
+      <c r="A6" s="7"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7">
         <v>11922025909</v>
       </c>
-      <c r="K6" s="8"/>
+      <c r="K6" s="7"/>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A7" s="8"/>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="17">
+      <c r="A7" s="7"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="14">
         <v>11922025908</v>
       </c>
-      <c r="K7" s="8"/>
+      <c r="K7" s="7"/>
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="J8" s="8">
+      <c r="J8" s="7">
         <v>11922025999</v>
       </c>
     </row>

--- a/Data/ON_Market.xlsx
+++ b/Data/ON_Market.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F723633-3DFB-46D0-AEA1-B5692C518605}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D87A9DE-F317-4EBB-9013-531FA36DD841}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="8520" windowHeight="10605" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settlement" sheetId="1" r:id="rId1"/>
@@ -150,7 +150,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="167" formatCode="dd\/mm\/yyyy"/>
+    <numFmt numFmtId="164" formatCode="dd\/mm\/yyyy"/>
   </numFmts>
   <fonts count="10" x14ac:knownFonts="1">
     <font>
@@ -301,8 +301,8 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>

--- a/Data/ON_Market.xlsx
+++ b/Data/ON_Market.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D87A9DE-F317-4EBB-9013-531FA36DD841}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9388A7F1-E063-4E3D-AF5F-5B49F40034BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="8520" windowHeight="10605" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settlement" sheetId="1" r:id="rId1"/>

--- a/Data/ON_Market.xlsx
+++ b/Data/ON_Market.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9388A7F1-E063-4E3D-AF5F-5B49F40034BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7491E0F9-AC44-4AF1-BF99-81F24C4A2040}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settlement" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="40">
   <si>
     <t>ExchangeMaster</t>
   </si>
@@ -143,6 +143,9 @@
   </si>
   <si>
     <t>Delivery_Marking_Day</t>
+  </si>
+  <si>
+    <t>1 - WHEAT</t>
   </si>
 </sst>
 </file>
@@ -950,27 +953,69 @@
       <c r="DN2" s="1"/>
     </row>
     <row r="3" spans="1:118" x14ac:dyDescent="0.25">
-      <c r="A3" s="4"/>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
-      <c r="N3" s="1"/>
-      <c r="O3" s="1"/>
-      <c r="P3" s="1"/>
-      <c r="Q3" s="1"/>
-      <c r="R3" s="1"/>
-      <c r="S3" s="1"/>
-      <c r="T3" s="1"/>
-      <c r="U3" s="6"/>
+      <c r="A3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="4">
+        <v>92</v>
+      </c>
+      <c r="C3" s="4">
+        <v>160</v>
+      </c>
+      <c r="D3" s="4">
+        <v>2025</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="F3" s="16">
+        <v>45961</v>
+      </c>
+      <c r="G3" s="15">
+        <v>45939</v>
+      </c>
+      <c r="H3" s="16">
+        <v>45961</v>
+      </c>
+      <c r="I3" s="15">
+        <v>45939</v>
+      </c>
+      <c r="J3" s="16">
+        <v>45961</v>
+      </c>
+      <c r="K3" s="1">
+        <v>4</v>
+      </c>
+      <c r="L3" s="1">
+        <v>4</v>
+      </c>
+      <c r="M3" s="16">
+        <v>45961</v>
+      </c>
+      <c r="N3" s="1">
+        <v>6</v>
+      </c>
+      <c r="O3" s="1">
+        <v>5</v>
+      </c>
+      <c r="P3" s="16">
+        <v>45955</v>
+      </c>
+      <c r="Q3" s="1">
+        <v>6</v>
+      </c>
+      <c r="R3" s="1">
+        <v>6</v>
+      </c>
+      <c r="S3" s="16">
+        <v>45955</v>
+      </c>
+      <c r="T3" s="1">
+        <v>7</v>
+      </c>
+      <c r="U3" s="6">
+        <v>7</v>
+      </c>
       <c r="V3" s="1"/>
       <c r="W3" s="1"/>
       <c r="X3" s="1"/>

--- a/Data/ON_Market.xlsx
+++ b/Data/ON_Market.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7491E0F9-AC44-4AF1-BF99-81F24C4A2040}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71228BFD-563F-49CB-9C54-DB6A5FD3EEB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settlement" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="42">
   <si>
     <t>ExchangeMaster</t>
   </si>
@@ -146,6 +146,12 @@
   </si>
   <si>
     <t>1 - WHEAT</t>
+  </si>
+  <si>
+    <t>07</t>
+  </si>
+  <si>
+    <t>06</t>
   </si>
 </sst>
 </file>
@@ -288,7 +294,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -306,6 +312,8 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -848,7 +856,7 @@
       <c r="S2" s="16">
         <v>45955</v>
       </c>
-      <c r="T2" s="1">
+      <c r="T2" s="18">
         <v>7</v>
       </c>
       <c r="U2" s="6">
@@ -1001,8 +1009,8 @@
       <c r="P3" s="16">
         <v>45955</v>
       </c>
-      <c r="Q3" s="1">
-        <v>6</v>
+      <c r="Q3" s="17" t="s">
+        <v>41</v>
       </c>
       <c r="R3" s="1">
         <v>6</v>
@@ -1010,8 +1018,8 @@
       <c r="S3" s="16">
         <v>45955</v>
       </c>
-      <c r="T3" s="1">
-        <v>7</v>
+      <c r="T3" s="17" t="s">
+        <v>40</v>
       </c>
       <c r="U3" s="6">
         <v>7</v>

--- a/Data/ON_Market.xlsx
+++ b/Data/ON_Market.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71228BFD-563F-49CB-9C54-DB6A5FD3EEB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D41F286E-A74D-47D9-B9CD-6CE9DD66AB27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="42">
   <si>
     <t>ExchangeMaster</t>
   </si>
@@ -294,7 +294,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -309,11 +309,10 @@
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -806,7 +805,7 @@
         <v>92</v>
       </c>
       <c r="C2" s="4">
-        <v>160</v>
+        <v>121</v>
       </c>
       <c r="D2" s="4">
         <v>2025</v>
@@ -814,19 +813,19 @@
       <c r="E2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="16">
+      <c r="F2" s="15">
         <v>45961</v>
       </c>
-      <c r="G2" s="15">
+      <c r="G2" s="14">
         <v>45939</v>
       </c>
-      <c r="H2" s="16">
+      <c r="H2" s="15">
         <v>45961</v>
       </c>
-      <c r="I2" s="15">
+      <c r="I2" s="14">
         <v>45939</v>
       </c>
-      <c r="J2" s="16">
+      <c r="J2" s="15">
         <v>45961</v>
       </c>
       <c r="K2" s="1">
@@ -835,7 +834,7 @@
       <c r="L2" s="1">
         <v>4</v>
       </c>
-      <c r="M2" s="16">
+      <c r="M2" s="15">
         <v>45961</v>
       </c>
       <c r="N2" s="1">
@@ -844,7 +843,7 @@
       <c r="O2" s="1">
         <v>5</v>
       </c>
-      <c r="P2" s="16">
+      <c r="P2" s="15">
         <v>45955</v>
       </c>
       <c r="Q2" s="1">
@@ -853,10 +852,10 @@
       <c r="R2" s="1">
         <v>6</v>
       </c>
-      <c r="S2" s="16">
+      <c r="S2" s="15">
         <v>45955</v>
       </c>
-      <c r="T2" s="18">
+      <c r="T2" s="1">
         <v>7</v>
       </c>
       <c r="U2" s="6">
@@ -976,19 +975,19 @@
       <c r="E3" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="F3" s="16">
+      <c r="F3" s="15">
         <v>45961</v>
       </c>
-      <c r="G3" s="15">
+      <c r="G3" s="14">
         <v>45939</v>
       </c>
-      <c r="H3" s="16">
+      <c r="H3" s="15">
         <v>45961</v>
       </c>
-      <c r="I3" s="15">
+      <c r="I3" s="14">
         <v>45939</v>
       </c>
-      <c r="J3" s="16">
+      <c r="J3" s="15">
         <v>45961</v>
       </c>
       <c r="K3" s="1">
@@ -997,7 +996,7 @@
       <c r="L3" s="1">
         <v>4</v>
       </c>
-      <c r="M3" s="16">
+      <c r="M3" s="15">
         <v>45961</v>
       </c>
       <c r="N3" s="1">
@@ -1006,19 +1005,19 @@
       <c r="O3" s="1">
         <v>5</v>
       </c>
-      <c r="P3" s="16">
+      <c r="P3" s="15">
         <v>45955</v>
       </c>
-      <c r="Q3" s="17" t="s">
+      <c r="Q3" s="16" t="s">
         <v>41</v>
       </c>
       <c r="R3" s="1">
         <v>6</v>
       </c>
-      <c r="S3" s="16">
+      <c r="S3" s="15">
         <v>45955</v>
       </c>
-      <c r="T3" s="17" t="s">
+      <c r="T3" s="16" t="s">
         <v>40</v>
       </c>
       <c r="U3" s="6">
@@ -1567,7 +1566,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9177B227-E92D-4A4F-80A9-A49FCFC71FB6}">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.5703125" customWidth="1"/>
@@ -1737,62 +1736,277 @@
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A5" s="7"/>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
-      <c r="I5" s="7"/>
+      <c r="A5" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" s="7">
+        <v>6666103</v>
+      </c>
+      <c r="C5" s="7">
+        <v>9999996</v>
+      </c>
+      <c r="D5" s="7">
+        <v>1000421</v>
+      </c>
+      <c r="E5" s="7">
+        <v>1</v>
+      </c>
+      <c r="F5" s="9">
+        <v>100673000000011</v>
+      </c>
+      <c r="G5" s="7">
+        <v>973015</v>
+      </c>
+      <c r="H5" s="9">
+        <v>400920251740</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>33</v>
+      </c>
       <c r="J5" s="7">
-        <v>11922025567</v>
-      </c>
-      <c r="K5" s="7"/>
+        <v>11922025121</v>
+      </c>
+      <c r="K5" s="17">
+        <v>110001031407</v>
+      </c>
       <c r="L5" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="M5" s="1"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A6" s="7"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
+      <c r="A6" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" s="7">
+        <v>6666103</v>
+      </c>
+      <c r="C6" s="7">
+        <v>9999996</v>
+      </c>
+      <c r="D6" s="7">
+        <v>1000421</v>
+      </c>
+      <c r="E6" s="7">
+        <v>1</v>
+      </c>
+      <c r="F6" s="9">
+        <v>100673000000011</v>
+      </c>
+      <c r="G6" s="7">
+        <v>973015</v>
+      </c>
+      <c r="H6" s="9">
+        <v>400920251740</v>
+      </c>
+      <c r="I6" s="9" t="s">
+        <v>33</v>
+      </c>
       <c r="J6" s="7">
         <v>11922025909</v>
       </c>
-      <c r="K6" s="7"/>
-      <c r="L6" s="1"/>
+      <c r="K6" s="17">
+        <v>110001031506</v>
+      </c>
+      <c r="L6" s="1">
+        <v>100</v>
+      </c>
       <c r="M6" s="1"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A7" s="7"/>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="7"/>
-      <c r="J7" s="14">
-        <v>11922025908</v>
-      </c>
-      <c r="K7" s="7"/>
-      <c r="L7" s="1"/>
+      <c r="A7" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" s="7">
+        <v>6666103</v>
+      </c>
+      <c r="C7" s="7">
+        <v>9999996</v>
+      </c>
+      <c r="D7" s="7">
+        <v>1000421</v>
+      </c>
+      <c r="E7" s="7">
+        <v>1</v>
+      </c>
+      <c r="F7" s="9">
+        <v>100673000000011</v>
+      </c>
+      <c r="G7" s="7">
+        <v>973015</v>
+      </c>
+      <c r="H7" s="9">
+        <v>400920251740</v>
+      </c>
+      <c r="I7" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="J7" s="7">
+        <v>11922025909</v>
+      </c>
+      <c r="K7" s="17">
+        <v>110001031480</v>
+      </c>
+      <c r="L7" s="1">
+        <v>100</v>
+      </c>
       <c r="M7" s="1"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A8" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" s="7">
+        <v>6666103</v>
+      </c>
+      <c r="C8" s="7">
+        <v>9999996</v>
+      </c>
+      <c r="D8" s="7">
+        <v>1000421</v>
+      </c>
+      <c r="E8" s="7">
+        <v>1</v>
+      </c>
+      <c r="F8" s="9">
+        <v>100673000000011</v>
+      </c>
+      <c r="G8" s="7">
+        <v>973015</v>
+      </c>
+      <c r="H8" s="9">
+        <v>400920251740</v>
+      </c>
+      <c r="I8" s="9" t="s">
+        <v>33</v>
+      </c>
       <c r="J8" s="7">
-        <v>11922025999</v>
-      </c>
+        <v>11922025909</v>
+      </c>
+      <c r="K8" s="17">
+        <v>110001031464</v>
+      </c>
+      <c r="L8" s="1">
+        <v>100</v>
+      </c>
+      <c r="M8" s="1"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A9" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" s="7">
+        <v>6666103</v>
+      </c>
+      <c r="C9" s="7">
+        <v>9999996</v>
+      </c>
+      <c r="D9" s="7">
+        <v>1000421</v>
+      </c>
+      <c r="E9" s="7">
+        <v>1</v>
+      </c>
+      <c r="F9" s="9">
+        <v>100673000000011</v>
+      </c>
+      <c r="G9" s="7">
+        <v>973015</v>
+      </c>
+      <c r="H9" s="9">
+        <v>400920251740</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="J9" s="7">
+        <v>11922025909</v>
+      </c>
+      <c r="K9" s="17">
+        <v>110001031449</v>
+      </c>
+      <c r="L9" s="1">
+        <v>100</v>
+      </c>
+      <c r="M9" s="1"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A10" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B10" s="7">
+        <v>6666103</v>
+      </c>
+      <c r="C10" s="7">
+        <v>9999996</v>
+      </c>
+      <c r="D10" s="7">
+        <v>1000421</v>
+      </c>
+      <c r="E10" s="7">
+        <v>1</v>
+      </c>
+      <c r="F10" s="9">
+        <v>100673000000011</v>
+      </c>
+      <c r="G10" s="7">
+        <v>973015</v>
+      </c>
+      <c r="H10" s="9">
+        <v>400920251740</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="J10" s="7">
+        <v>11922025909</v>
+      </c>
+      <c r="K10" s="17">
+        <v>110001031381</v>
+      </c>
+      <c r="L10" s="1">
+        <v>100</v>
+      </c>
+      <c r="M10" s="1"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A11" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" s="7">
+        <v>6666103</v>
+      </c>
+      <c r="C11" s="7">
+        <v>9999996</v>
+      </c>
+      <c r="D11" s="7">
+        <v>1000421</v>
+      </c>
+      <c r="E11" s="7">
+        <v>1</v>
+      </c>
+      <c r="F11" s="9">
+        <v>100673000000011</v>
+      </c>
+      <c r="G11" s="7">
+        <v>973015</v>
+      </c>
+      <c r="H11" s="9">
+        <v>400920251740</v>
+      </c>
+      <c r="I11" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="J11" s="7">
+        <v>11922025909</v>
+      </c>
+      <c r="K11" s="17">
+        <v>110001031423</v>
+      </c>
+      <c r="L11" s="1">
+        <v>100</v>
+      </c>
+      <c r="M11" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Data/ON_Market.xlsx
+++ b/Data/ON_Market.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D41F286E-A74D-47D9-B9CD-6CE9DD66AB27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FA38220-8394-4BBA-932E-CB3589AE43F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settlement" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="40">
   <si>
     <t>ExchangeMaster</t>
   </si>
@@ -146,12 +146,6 @@
   </si>
   <si>
     <t>1 - WHEAT</t>
-  </si>
-  <si>
-    <t>07</t>
-  </si>
-  <si>
-    <t>06</t>
   </si>
 </sst>
 </file>
@@ -294,11 +288,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -311,8 +304,8 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -613,7 +606,7 @@
     <col min="15" max="15" width="17.28515625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="23.42578125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="22.42578125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="21.42578125" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="20.85546875" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="24" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="24.42578125" bestFit="1" customWidth="1"/>
@@ -651,58 +644,58 @@
       <c r="E1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="H1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="I1" s="13" t="s">
+      <c r="I1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="J1" s="13" t="s">
+      <c r="J1" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="13" t="s">
+      <c r="K1" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="13" t="s">
+      <c r="L1" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="13" t="s">
+      <c r="M1" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="13" t="s">
+      <c r="N1" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="13" t="s">
+      <c r="O1" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="13" t="s">
+      <c r="P1" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="13" t="s">
+      <c r="Q1" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="R1" s="13" t="s">
+      <c r="R1" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="S1" s="8" t="s">
+      <c r="S1" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="T1" s="8" t="s">
+      <c r="T1" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="U1" s="13" t="s">
+      <c r="U1" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="V1" s="5"/>
-      <c r="W1" s="12"/>
+      <c r="V1" s="4"/>
+      <c r="W1" s="11"/>
       <c r="X1" s="1"/>
-      <c r="Y1" s="12"/>
+      <c r="Y1" s="11"/>
       <c r="Z1" s="1"/>
       <c r="AA1" s="1"/>
       <c r="AB1" s="1"/>
@@ -798,35 +791,35 @@
       <c r="DN1" s="1"/>
     </row>
     <row r="2" spans="1:118" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="4">
+      <c r="B2" s="3">
         <v>92</v>
       </c>
-      <c r="C2" s="4">
+      <c r="C2" s="3">
         <v>121</v>
       </c>
-      <c r="D2" s="4">
+      <c r="D2" s="3">
         <v>2025</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="15">
-        <v>45961</v>
-      </c>
-      <c r="G2" s="14">
-        <v>45939</v>
-      </c>
-      <c r="H2" s="15">
-        <v>45961</v>
-      </c>
-      <c r="I2" s="14">
-        <v>45939</v>
-      </c>
-      <c r="J2" s="15">
-        <v>45961</v>
+      <c r="F2" s="14">
+        <v>46021</v>
+      </c>
+      <c r="G2" s="13">
+        <v>46000</v>
+      </c>
+      <c r="H2" s="14">
+        <v>46021</v>
+      </c>
+      <c r="I2" s="13">
+        <v>46000</v>
+      </c>
+      <c r="J2" s="14">
+        <v>46021</v>
       </c>
       <c r="K2" s="1">
         <v>4</v>
@@ -834,8 +827,8 @@
       <c r="L2" s="1">
         <v>4</v>
       </c>
-      <c r="M2" s="15">
-        <v>45961</v>
+      <c r="M2" s="14">
+        <v>46021</v>
       </c>
       <c r="N2" s="1">
         <v>6</v>
@@ -843,8 +836,8 @@
       <c r="O2" s="1">
         <v>5</v>
       </c>
-      <c r="P2" s="15">
-        <v>45955</v>
+      <c r="P2" s="14">
+        <v>45993</v>
       </c>
       <c r="Q2" s="1">
         <v>6</v>
@@ -852,13 +845,13 @@
       <c r="R2" s="1">
         <v>6</v>
       </c>
-      <c r="S2" s="15">
-        <v>45955</v>
+      <c r="S2" s="14">
+        <v>45993</v>
       </c>
       <c r="T2" s="1">
         <v>7</v>
       </c>
-      <c r="U2" s="6">
+      <c r="U2" s="5">
         <v>7</v>
       </c>
       <c r="V2" s="1"/>
@@ -960,34 +953,34 @@
       <c r="DN2" s="1"/>
     </row>
     <row r="3" spans="1:118" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="B3" s="4">
+      <c r="B3" s="3">
         <v>92</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C3" s="3">
         <v>160</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D3" s="3">
         <v>2025</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="F3" s="15">
+      <c r="F3" s="14">
         <v>45961</v>
       </c>
-      <c r="G3" s="14">
+      <c r="G3" s="13">
         <v>45939</v>
       </c>
-      <c r="H3" s="15">
+      <c r="H3" s="14">
         <v>45961</v>
       </c>
-      <c r="I3" s="14">
+      <c r="I3" s="13">
         <v>45939</v>
       </c>
-      <c r="J3" s="15">
+      <c r="J3" s="14">
         <v>45961</v>
       </c>
       <c r="K3" s="1">
@@ -996,7 +989,7 @@
       <c r="L3" s="1">
         <v>4</v>
       </c>
-      <c r="M3" s="15">
+      <c r="M3" s="14">
         <v>45961</v>
       </c>
       <c r="N3" s="1">
@@ -1005,22 +998,22 @@
       <c r="O3" s="1">
         <v>5</v>
       </c>
-      <c r="P3" s="15">
+      <c r="P3" s="14">
         <v>45955</v>
       </c>
-      <c r="Q3" s="16" t="s">
-        <v>41</v>
+      <c r="Q3" s="1">
+        <v>6</v>
       </c>
       <c r="R3" s="1">
         <v>6</v>
       </c>
-      <c r="S3" s="15">
+      <c r="S3" s="14">
         <v>45955</v>
       </c>
-      <c r="T3" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="U3" s="6">
+      <c r="T3" s="1">
+        <v>7</v>
+      </c>
+      <c r="U3" s="5">
         <v>7</v>
       </c>
       <c r="V3" s="1"/>
@@ -1122,12 +1115,12 @@
       <c r="DN3" s="1"/>
     </row>
     <row r="4" spans="1:118" x14ac:dyDescent="0.25">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
@@ -1142,7 +1135,7 @@
       <c r="R4" s="1"/>
       <c r="S4" s="1"/>
       <c r="T4" s="1"/>
-      <c r="U4" s="6"/>
+      <c r="U4" s="5"/>
       <c r="V4" s="1"/>
       <c r="W4" s="1"/>
       <c r="X4" s="1"/>
@@ -1242,12 +1235,12 @@
       <c r="DN4" s="1"/>
     </row>
     <row r="5" spans="1:118" x14ac:dyDescent="0.25">
-      <c r="A5" s="4"/>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
+      <c r="A5" s="3"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
@@ -1262,7 +1255,7 @@
       <c r="R5" s="1"/>
       <c r="S5" s="1"/>
       <c r="T5" s="1"/>
-      <c r="U5" s="6"/>
+      <c r="U5" s="5"/>
       <c r="V5" s="1"/>
       <c r="W5" s="1"/>
       <c r="X5" s="1"/>
@@ -1578,195 +1571,195 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="I1" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="J1" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="K1" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="L1" s="10" t="s">
+      <c r="L1" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="M1" s="11" t="s">
+      <c r="M1" s="10" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B2" s="7">
+      <c r="B2" s="6">
         <v>6666101</v>
       </c>
-      <c r="C2" s="7">
+      <c r="C2" s="6">
         <v>9999996</v>
       </c>
-      <c r="D2" s="7">
+      <c r="D2" s="6">
         <v>1000421</v>
       </c>
-      <c r="E2" s="7">
+      <c r="E2" s="6">
         <v>15</v>
       </c>
-      <c r="F2" s="9">
+      <c r="F2" s="8">
         <v>100673000000011</v>
       </c>
-      <c r="G2" s="7">
+      <c r="G2" s="6">
         <v>973015</v>
       </c>
-      <c r="H2" s="9">
+      <c r="H2" s="8">
         <v>400920251740</v>
       </c>
-      <c r="I2" s="9" t="s">
+      <c r="I2" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="J2" s="7">
+      <c r="J2" s="6">
         <v>11922025567</v>
       </c>
-      <c r="K2" s="9">
+      <c r="K2" s="8">
         <v>110001017786</v>
       </c>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="6">
         <v>6666102</v>
       </c>
-      <c r="C3" s="7">
+      <c r="C3" s="6">
         <v>9996059</v>
       </c>
-      <c r="D3" s="7">
+      <c r="D3" s="6">
         <v>5750013</v>
       </c>
-      <c r="E3" s="7">
+      <c r="E3" s="6">
         <v>15</v>
       </c>
-      <c r="F3" s="9">
+      <c r="F3" s="8">
         <v>100673000000011</v>
       </c>
-      <c r="G3" s="7">
+      <c r="G3" s="6">
         <v>973015</v>
       </c>
-      <c r="H3" s="9">
+      <c r="H3" s="8">
         <v>400920251740</v>
       </c>
-      <c r="I3" s="9" t="s">
+      <c r="I3" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="J3" s="7">
+      <c r="J3" s="6">
         <v>11922025160</v>
       </c>
-      <c r="K3" s="9">
+      <c r="K3" s="8">
         <v>110001017943</v>
       </c>
-      <c r="L3" s="9">
+      <c r="L3" s="8">
         <v>100</v>
       </c>
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4" s="6">
         <v>6666103</v>
       </c>
-      <c r="C4" s="7">
+      <c r="C4" s="6">
         <v>9999996</v>
       </c>
-      <c r="D4" s="7">
+      <c r="D4" s="6">
         <v>1000421</v>
       </c>
-      <c r="E4" s="7">
+      <c r="E4" s="6">
         <v>1</v>
       </c>
-      <c r="F4" s="9">
+      <c r="F4" s="8">
         <v>100673000000011</v>
       </c>
-      <c r="G4" s="7">
+      <c r="G4" s="6">
         <v>973015</v>
       </c>
-      <c r="H4" s="9">
+      <c r="H4" s="8">
         <v>400920251740</v>
       </c>
-      <c r="I4" s="9" t="s">
+      <c r="I4" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="J4" s="7">
+      <c r="J4" s="6">
         <v>11922025909</v>
       </c>
-      <c r="K4" s="9">
+      <c r="K4" s="8">
         <v>110001023792</v>
       </c>
       <c r="L4" s="1">
         <v>100</v>
       </c>
-      <c r="M4" s="9">
+      <c r="M4" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="6">
         <v>6666103</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="6">
         <v>9999996</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5" s="6">
         <v>1000421</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5" s="6">
         <v>1</v>
       </c>
-      <c r="F5" s="9">
+      <c r="F5" s="8">
         <v>100673000000011</v>
       </c>
-      <c r="G5" s="7">
+      <c r="G5" s="6">
         <v>973015</v>
       </c>
-      <c r="H5" s="9">
+      <c r="H5" s="8">
         <v>400920251740</v>
       </c>
-      <c r="I5" s="9" t="s">
+      <c r="I5" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="J5" s="7">
+      <c r="J5" s="6">
         <v>11922025121</v>
       </c>
-      <c r="K5" s="17">
+      <c r="K5" s="15">
         <v>110001031407</v>
       </c>
       <c r="L5" s="1">
@@ -1775,37 +1768,37 @@
       <c r="M5" s="1"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="6">
         <v>6666103</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="6">
         <v>9999996</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="6">
         <v>1000421</v>
       </c>
-      <c r="E6" s="7">
+      <c r="E6" s="6">
         <v>1</v>
       </c>
-      <c r="F6" s="9">
+      <c r="F6" s="8">
         <v>100673000000011</v>
       </c>
-      <c r="G6" s="7">
+      <c r="G6" s="6">
         <v>973015</v>
       </c>
-      <c r="H6" s="9">
+      <c r="H6" s="8">
         <v>400920251740</v>
       </c>
-      <c r="I6" s="9" t="s">
+      <c r="I6" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="J6" s="7">
+      <c r="J6" s="6">
         <v>11922025909</v>
       </c>
-      <c r="K6" s="17">
+      <c r="K6" s="15">
         <v>110001031506</v>
       </c>
       <c r="L6" s="1">
@@ -1814,37 +1807,37 @@
       <c r="M6" s="1"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7" s="6">
         <v>6666103</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C7" s="6">
         <v>9999996</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="6">
         <v>1000421</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E7" s="6">
         <v>1</v>
       </c>
-      <c r="F7" s="9">
+      <c r="F7" s="8">
         <v>100673000000011</v>
       </c>
-      <c r="G7" s="7">
+      <c r="G7" s="6">
         <v>973015</v>
       </c>
-      <c r="H7" s="9">
+      <c r="H7" s="8">
         <v>400920251740</v>
       </c>
-      <c r="I7" s="9" t="s">
+      <c r="I7" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="J7" s="7">
+      <c r="J7" s="6">
         <v>11922025909</v>
       </c>
-      <c r="K7" s="17">
+      <c r="K7" s="15">
         <v>110001031480</v>
       </c>
       <c r="L7" s="1">
@@ -1853,37 +1846,37 @@
       <c r="M7" s="1"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B8" s="6">
         <v>6666103</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="6">
         <v>9999996</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="6">
         <v>1000421</v>
       </c>
-      <c r="E8" s="7">
+      <c r="E8" s="6">
         <v>1</v>
       </c>
-      <c r="F8" s="9">
+      <c r="F8" s="8">
         <v>100673000000011</v>
       </c>
-      <c r="G8" s="7">
+      <c r="G8" s="6">
         <v>973015</v>
       </c>
-      <c r="H8" s="9">
+      <c r="H8" s="8">
         <v>400920251740</v>
       </c>
-      <c r="I8" s="9" t="s">
+      <c r="I8" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="J8" s="7">
+      <c r="J8" s="6">
         <v>11922025909</v>
       </c>
-      <c r="K8" s="17">
+      <c r="K8" s="15">
         <v>110001031464</v>
       </c>
       <c r="L8" s="1">
@@ -1892,37 +1885,37 @@
       <c r="M8" s="1"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B9" s="6">
         <v>6666103</v>
       </c>
-      <c r="C9" s="7">
+      <c r="C9" s="6">
         <v>9999996</v>
       </c>
-      <c r="D9" s="7">
+      <c r="D9" s="6">
         <v>1000421</v>
       </c>
-      <c r="E9" s="7">
+      <c r="E9" s="6">
         <v>1</v>
       </c>
-      <c r="F9" s="9">
+      <c r="F9" s="8">
         <v>100673000000011</v>
       </c>
-      <c r="G9" s="7">
+      <c r="G9" s="6">
         <v>973015</v>
       </c>
-      <c r="H9" s="9">
+      <c r="H9" s="8">
         <v>400920251740</v>
       </c>
-      <c r="I9" s="9" t="s">
+      <c r="I9" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="J9" s="7">
+      <c r="J9" s="6">
         <v>11922025909</v>
       </c>
-      <c r="K9" s="17">
+      <c r="K9" s="15">
         <v>110001031449</v>
       </c>
       <c r="L9" s="1">
@@ -1931,37 +1924,37 @@
       <c r="M9" s="1"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B10" s="7">
+      <c r="B10" s="6">
         <v>6666103</v>
       </c>
-      <c r="C10" s="7">
+      <c r="C10" s="6">
         <v>9999996</v>
       </c>
-      <c r="D10" s="7">
+      <c r="D10" s="6">
         <v>1000421</v>
       </c>
-      <c r="E10" s="7">
+      <c r="E10" s="6">
         <v>1</v>
       </c>
-      <c r="F10" s="9">
+      <c r="F10" s="8">
         <v>100673000000011</v>
       </c>
-      <c r="G10" s="7">
+      <c r="G10" s="6">
         <v>973015</v>
       </c>
-      <c r="H10" s="9">
+      <c r="H10" s="8">
         <v>400920251740</v>
       </c>
-      <c r="I10" s="9" t="s">
+      <c r="I10" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="J10" s="7">
+      <c r="J10" s="6">
         <v>11922025909</v>
       </c>
-      <c r="K10" s="17">
+      <c r="K10" s="15">
         <v>110001031381</v>
       </c>
       <c r="L10" s="1">
@@ -1970,37 +1963,37 @@
       <c r="M10" s="1"/>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B11" s="7">
+      <c r="B11" s="6">
         <v>6666103</v>
       </c>
-      <c r="C11" s="7">
+      <c r="C11" s="6">
         <v>9999996</v>
       </c>
-      <c r="D11" s="7">
+      <c r="D11" s="6">
         <v>1000421</v>
       </c>
-      <c r="E11" s="7">
+      <c r="E11" s="6">
         <v>1</v>
       </c>
-      <c r="F11" s="9">
+      <c r="F11" s="8">
         <v>100673000000011</v>
       </c>
-      <c r="G11" s="7">
+      <c r="G11" s="6">
         <v>973015</v>
       </c>
-      <c r="H11" s="9">
+      <c r="H11" s="8">
         <v>400920251740</v>
       </c>
-      <c r="I11" s="9" t="s">
+      <c r="I11" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="J11" s="7">
+      <c r="J11" s="6">
         <v>11922025909</v>
       </c>
-      <c r="K11" s="17">
+      <c r="K11" s="15">
         <v>110001031423</v>
       </c>
       <c r="L11" s="1">

--- a/Data/ON_Market.xlsx
+++ b/Data/ON_Market.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FA38220-8394-4BBA-932E-CB3589AE43F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9412818-ED96-464A-B1A6-C06DEC63487D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="41">
   <si>
     <t>ExchangeMaster</t>
   </si>
@@ -146,6 +146,9 @@
   </si>
   <si>
     <t>1 - WHEAT</t>
+  </si>
+  <si>
+    <t>1003 - ZINC</t>
   </si>
 </sst>
 </file>
@@ -155,7 +158,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd\/mm\/yyyy"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -220,6 +223,13 @@
       <color rgb="FF2A314A"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="5">
@@ -288,7 +298,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -306,6 +316,7 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -798,19 +809,19 @@
         <v>92</v>
       </c>
       <c r="C2" s="3">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="D2" s="3">
         <v>2025</v>
       </c>
-      <c r="E2" s="4" t="s">
-        <v>7</v>
+      <c r="E2" s="17" t="s">
+        <v>40</v>
       </c>
       <c r="F2" s="14">
         <v>46021</v>
       </c>
       <c r="G2" s="13">
-        <v>46000</v>
+        <v>45993</v>
       </c>
       <c r="H2" s="14">
         <v>46021</v>
@@ -1119,7 +1130,9 @@
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
+      <c r="E4" s="4" t="s">
+        <v>7</v>
+      </c>
       <c r="F4" s="3"/>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
@@ -1239,7 +1252,9 @@
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
+      <c r="E5" s="17" t="s">
+        <v>40</v>
+      </c>
       <c r="F5" s="3"/>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>

--- a/Data/ON_Market.xlsx
+++ b/Data/ON_Market.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9412818-ED96-464A-B1A6-C06DEC63487D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B70939F-0E05-4CFE-8F54-82D153BEC09B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Data/ON_Market.xlsx
+++ b/Data/ON_Market.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B70939F-0E05-4CFE-8F54-82D153BEC09B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B6A7574-49E5-45C4-B1D5-B8EF7648F5BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -809,7 +809,7 @@
         <v>92</v>
       </c>
       <c r="C2" s="3">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D2" s="3">
         <v>2025</v>
@@ -821,13 +821,13 @@
         <v>46021</v>
       </c>
       <c r="G2" s="13">
-        <v>45993</v>
+        <v>46001</v>
       </c>
       <c r="H2" s="14">
         <v>46021</v>
       </c>
       <c r="I2" s="13">
-        <v>46000</v>
+        <v>46010</v>
       </c>
       <c r="J2" s="14">
         <v>46021</v>
@@ -848,7 +848,7 @@
         <v>5</v>
       </c>
       <c r="P2" s="14">
-        <v>45993</v>
+        <v>46001</v>
       </c>
       <c r="Q2" s="1">
         <v>6</v>
@@ -857,7 +857,7 @@
         <v>6</v>
       </c>
       <c r="S2" s="14">
-        <v>45993</v>
+        <v>46001</v>
       </c>
       <c r="T2" s="1">
         <v>7</v>

--- a/Data/ON_Market.xlsx
+++ b/Data/ON_Market.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B6A7574-49E5-45C4-B1D5-B8EF7648F5BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F944300-E090-4CCA-A437-FEC73DB2C5B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,9 +40,6 @@
     <t>settlement_Year</t>
   </si>
   <si>
-    <t>expectedDay</t>
-  </si>
-  <si>
     <t>trade_Day</t>
   </si>
   <si>
@@ -149,6 +146,9 @@
   </si>
   <si>
     <t>1003 - ZINC</t>
+  </si>
+  <si>
+    <t>Contract Expiry Date</t>
   </si>
 </sst>
 </file>
@@ -653,55 +653,55 @@
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F1" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="12" t="s">
-        <v>5</v>
-      </c>
       <c r="H1" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="I1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="I1" s="12" t="s">
-        <v>38</v>
-      </c>
       <c r="J1" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="K1" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="12" t="s">
+      <c r="L1" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="12" t="s">
+      <c r="M1" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="12" t="s">
+      <c r="N1" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="12" t="s">
+      <c r="O1" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="12" t="s">
+      <c r="P1" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="12" t="s">
+      <c r="Q1" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="12" t="s">
+      <c r="R1" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="R1" s="12" t="s">
+      <c r="S1" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="S1" s="7" t="s">
+      <c r="T1" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="T1" s="7" t="s">
+      <c r="U1" s="12" t="s">
         <v>18</v>
-      </c>
-      <c r="U1" s="12" t="s">
-        <v>19</v>
       </c>
       <c r="V1" s="4"/>
       <c r="W1" s="11"/>
@@ -803,34 +803,34 @@
     </row>
     <row r="2" spans="1:118" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B2" s="3">
         <v>92</v>
       </c>
       <c r="C2" s="3">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D2" s="3">
         <v>2025</v>
       </c>
       <c r="E2" s="17" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F2" s="14">
-        <v>46021</v>
+        <v>46032</v>
       </c>
       <c r="G2" s="13">
-        <v>46001</v>
+        <v>46042</v>
       </c>
       <c r="H2" s="14">
-        <v>46021</v>
+        <v>46052</v>
       </c>
       <c r="I2" s="13">
-        <v>46010</v>
+        <v>46072</v>
       </c>
       <c r="J2" s="14">
-        <v>46021</v>
+        <v>46066</v>
       </c>
       <c r="K2" s="1">
         <v>4</v>
@@ -839,7 +839,7 @@
         <v>4</v>
       </c>
       <c r="M2" s="14">
-        <v>46021</v>
+        <v>46063</v>
       </c>
       <c r="N2" s="1">
         <v>6</v>
@@ -848,7 +848,7 @@
         <v>5</v>
       </c>
       <c r="P2" s="14">
-        <v>46001</v>
+        <v>46063</v>
       </c>
       <c r="Q2" s="1">
         <v>6</v>
@@ -857,7 +857,7 @@
         <v>6</v>
       </c>
       <c r="S2" s="14">
-        <v>46001</v>
+        <v>46063</v>
       </c>
       <c r="T2" s="1">
         <v>7</v>
@@ -965,7 +965,7 @@
     </row>
     <row r="3" spans="1:118" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B3" s="3">
         <v>92</v>
@@ -977,7 +977,7 @@
         <v>2025</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F3" s="14">
         <v>45961</v>
@@ -1131,7 +1131,7 @@
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
       <c r="E4" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F4" s="3"/>
       <c r="G4" s="1"/>
@@ -1253,7 +1253,7 @@
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
       <c r="E5" s="17" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F5" s="3"/>
       <c r="G5" s="1"/>
@@ -1587,48 +1587,48 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="C1" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="D1" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="E1" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="F1" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="G1" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="H1" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="I1" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="J1" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="K1" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="K1" s="7" t="s">
-        <v>31</v>
-      </c>
       <c r="L1" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M1" s="10" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B2" s="6">
         <v>6666101</v>
@@ -1652,7 +1652,7 @@
         <v>400920251740</v>
       </c>
       <c r="I2" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J2" s="6">
         <v>11922025567</v>
@@ -1665,7 +1665,7 @@
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B3" s="6">
         <v>6666102</v>
@@ -1689,7 +1689,7 @@
         <v>400920251740</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J3" s="6">
         <v>11922025160</v>
@@ -1704,7 +1704,7 @@
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B4" s="6">
         <v>6666103</v>
@@ -1728,7 +1728,7 @@
         <v>400920251740</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J4" s="6">
         <v>11922025909</v>
@@ -1745,7 +1745,7 @@
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B5" s="6">
         <v>6666103</v>
@@ -1769,7 +1769,7 @@
         <v>400920251740</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J5" s="6">
         <v>11922025121</v>
@@ -1784,7 +1784,7 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B6" s="6">
         <v>6666103</v>
@@ -1808,7 +1808,7 @@
         <v>400920251740</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J6" s="6">
         <v>11922025909</v>
@@ -1823,7 +1823,7 @@
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B7" s="6">
         <v>6666103</v>
@@ -1847,7 +1847,7 @@
         <v>400920251740</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J7" s="6">
         <v>11922025909</v>
@@ -1862,7 +1862,7 @@
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B8" s="6">
         <v>6666103</v>
@@ -1886,7 +1886,7 @@
         <v>400920251740</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J8" s="6">
         <v>11922025909</v>
@@ -1901,7 +1901,7 @@
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B9" s="6">
         <v>6666103</v>
@@ -1925,7 +1925,7 @@
         <v>400920251740</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J9" s="6">
         <v>11922025909</v>
@@ -1940,7 +1940,7 @@
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B10" s="6">
         <v>6666103</v>
@@ -1964,7 +1964,7 @@
         <v>400920251740</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J10" s="6">
         <v>11922025909</v>
@@ -1979,7 +1979,7 @@
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B11" s="6">
         <v>6666103</v>
@@ -2003,7 +2003,7 @@
         <v>400920251740</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J11" s="6">
         <v>11922025909</v>

--- a/Data/ON_Market.xlsx
+++ b/Data/ON_Market.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F944300-E090-4CCA-A437-FEC73DB2C5B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CBF37EA-F097-4D67-8B31-6C0A55136DBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="45">
   <si>
     <t>ExchangeMaster</t>
   </si>
@@ -49,18 +49,12 @@
     <t>15 - COTTON BALES</t>
   </si>
   <si>
-    <t>pay_In_date</t>
-  </si>
-  <si>
     <t>pay_In_Date_hr</t>
   </si>
   <si>
     <t>pay_In_Date_mn</t>
   </si>
   <si>
-    <t>pay_out_date</t>
-  </si>
-  <si>
     <t>pay_out_Date_hr</t>
   </si>
   <si>
@@ -142,13 +136,31 @@
     <t>Delivery_Marking_Day</t>
   </si>
   <si>
-    <t>1 - WHEAT</t>
-  </si>
-  <si>
     <t>1003 - ZINC</t>
   </si>
   <si>
     <t>Contract Expiry Date</t>
+  </si>
+  <si>
+    <t>947 - MENTHA OIL</t>
+  </si>
+  <si>
+    <t>SYMBOL</t>
+  </si>
+  <si>
+    <t>ZINC</t>
+  </si>
+  <si>
+    <t>Normal Payin End Date</t>
+  </si>
+  <si>
+    <t>Normal Payin End Time</t>
+  </si>
+  <si>
+    <t>MENTHAOIL</t>
+  </si>
+  <si>
+    <t>COTTONBALES</t>
   </si>
 </sst>
 </file>
@@ -298,7 +310,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -317,6 +329,7 @@
     <xf numFmtId="1" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -597,7 +610,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:DN7"/>
+  <dimension ref="A1:DO7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
@@ -605,41 +618,42 @@
     <col min="3" max="3" width="14.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="24.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.85546875" customWidth="1"/>
-    <col min="13" max="13" width="14.28515625" customWidth="1"/>
-    <col min="14" max="14" width="25.5703125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="23.42578125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="22.42578125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="24" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="24.42578125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="20.5703125" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="22.85546875" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="24" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.28515625" customWidth="1"/>
+    <col min="7" max="7" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.85546875" customWidth="1"/>
+    <col min="14" max="14" width="14.28515625" customWidth="1"/>
+    <col min="15" max="15" width="25.5703125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="20.85546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="24" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="20.85546875" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="24" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:118" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:119" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -655,59 +669,61 @@
       <c r="E1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="12" t="s">
-        <v>40</v>
+      <c r="F1" s="2" t="s">
+        <v>39</v>
       </c>
       <c r="G1" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="H1" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="12" t="s">
-        <v>36</v>
-      </c>
       <c r="I1" s="12" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="J1" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="K1" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="L1" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="12" t="s">
+      <c r="M1" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="12" t="s">
+      <c r="N1" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="O1" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="M1" s="12" t="s">
+      <c r="P1" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="N1" s="12" t="s">
+      <c r="Q1" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="O1" s="12" t="s">
+      <c r="R1" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="P1" s="12" t="s">
+      <c r="S1" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="Q1" s="12" t="s">
+      <c r="T1" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="R1" s="12" t="s">
+      <c r="U1" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="S1" s="7" t="s">
+      <c r="V1" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="T1" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="U1" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="V1" s="4"/>
-      <c r="W1" s="11"/>
-      <c r="X1" s="1"/>
-      <c r="Y1" s="11"/>
-      <c r="Z1" s="1"/>
+      <c r="W1" s="4"/>
+      <c r="X1" s="11"/>
+      <c r="Y1" s="1"/>
+      <c r="Z1" s="11"/>
       <c r="AA1" s="1"/>
       <c r="AB1" s="1"/>
       <c r="AC1" s="1"/>
@@ -800,72 +816,75 @@
       <c r="DL1" s="1"/>
       <c r="DM1" s="1"/>
       <c r="DN1" s="1"/>
+      <c r="DO1" s="1"/>
     </row>
-    <row r="2" spans="1:118" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:119" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="B2" s="3">
-        <v>92</v>
+        <v>17</v>
+      </c>
+      <c r="B2" s="18">
+        <v>1</v>
       </c>
       <c r="C2" s="3">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D2" s="3">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E2" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="F2" s="14">
-        <v>46032</v>
-      </c>
-      <c r="G2" s="13">
+        <v>36</v>
+      </c>
+      <c r="F2" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="G2" s="14">
+        <v>46081</v>
+      </c>
+      <c r="H2" s="13">
         <v>46042</v>
       </c>
-      <c r="H2" s="14">
-        <v>46052</v>
-      </c>
-      <c r="I2" s="13">
-        <v>46072</v>
-      </c>
-      <c r="J2" s="14">
-        <v>46066</v>
-      </c>
-      <c r="K2" s="1">
+      <c r="I2" s="14">
+        <v>46096</v>
+      </c>
+      <c r="J2" s="13">
+        <v>46078</v>
+      </c>
+      <c r="K2" s="13">
+        <v>46083</v>
+      </c>
+      <c r="L2" s="1">
+        <v>18</v>
+      </c>
+      <c r="M2" s="1">
         <v>4</v>
       </c>
-      <c r="L2" s="1">
-        <v>4</v>
-      </c>
-      <c r="M2" s="14">
-        <v>46063</v>
-      </c>
-      <c r="N2" s="1">
-        <v>6</v>
+      <c r="N2" s="13">
+        <v>46080</v>
       </c>
       <c r="O2" s="1">
-        <v>5</v>
-      </c>
-      <c r="P2" s="14">
-        <v>46063</v>
-      </c>
-      <c r="Q2" s="1">
-        <v>6</v>
+        <v>14</v>
+      </c>
+      <c r="P2" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="13">
+        <v>46042</v>
       </c>
       <c r="R2" s="1">
-        <v>6</v>
-      </c>
-      <c r="S2" s="14">
-        <v>46063</v>
-      </c>
-      <c r="T2" s="1">
-        <v>7</v>
-      </c>
-      <c r="U2" s="5">
-        <v>7</v>
-      </c>
-      <c r="V2" s="1"/>
+        <v>10</v>
+      </c>
+      <c r="S2" s="1">
+        <v>0</v>
+      </c>
+      <c r="T2" s="13">
+        <v>46083</v>
+      </c>
+      <c r="U2" s="1">
+        <v>10</v>
+      </c>
+      <c r="V2" s="5">
+        <v>59</v>
+      </c>
       <c r="W2" s="1"/>
       <c r="X2" s="1"/>
       <c r="Y2" s="1"/>
@@ -962,72 +981,75 @@
       <c r="DL2" s="1"/>
       <c r="DM2" s="1"/>
       <c r="DN2" s="1"/>
+      <c r="DO2" s="1"/>
     </row>
-    <row r="3" spans="1:118" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:119" x14ac:dyDescent="0.25">
       <c r="A3" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="B3" s="3">
-        <v>92</v>
+        <v>17</v>
+      </c>
+      <c r="B3" s="18">
+        <v>2</v>
       </c>
       <c r="C3" s="3">
-        <v>160</v>
+        <v>130</v>
       </c>
       <c r="D3" s="3">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="F3" s="14">
-        <v>45961</v>
-      </c>
-      <c r="G3" s="13">
-        <v>45939</v>
-      </c>
-      <c r="H3" s="14">
-        <v>45961</v>
-      </c>
-      <c r="I3" s="13">
-        <v>45939</v>
-      </c>
-      <c r="J3" s="14">
-        <v>45961</v>
-      </c>
-      <c r="K3" s="1">
+      <c r="F3" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="G3" s="14">
+        <v>46081</v>
+      </c>
+      <c r="H3" s="13">
+        <v>46042</v>
+      </c>
+      <c r="I3" s="14">
+        <v>46096</v>
+      </c>
+      <c r="J3" s="13">
+        <v>46078</v>
+      </c>
+      <c r="K3" s="13">
+        <v>46083</v>
+      </c>
+      <c r="L3" s="1">
+        <v>18</v>
+      </c>
+      <c r="M3" s="1">
         <v>4</v>
       </c>
-      <c r="L3" s="1">
-        <v>4</v>
-      </c>
-      <c r="M3" s="14">
-        <v>45961</v>
-      </c>
-      <c r="N3" s="1">
-        <v>6</v>
+      <c r="N3" s="13">
+        <v>46080</v>
       </c>
       <c r="O3" s="1">
-        <v>5</v>
-      </c>
-      <c r="P3" s="14">
-        <v>45955</v>
-      </c>
-      <c r="Q3" s="1">
-        <v>6</v>
+        <v>14</v>
+      </c>
+      <c r="P3" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="13">
+        <v>46042</v>
       </c>
       <c r="R3" s="1">
-        <v>6</v>
-      </c>
-      <c r="S3" s="14">
-        <v>45955</v>
-      </c>
-      <c r="T3" s="1">
-        <v>7</v>
-      </c>
-      <c r="U3" s="5">
-        <v>7</v>
-      </c>
-      <c r="V3" s="1"/>
+        <v>10</v>
+      </c>
+      <c r="S3" s="1">
+        <v>0</v>
+      </c>
+      <c r="T3" s="13">
+        <v>46083</v>
+      </c>
+      <c r="U3" s="1">
+        <v>10</v>
+      </c>
+      <c r="V3" s="5">
+        <v>59</v>
+      </c>
       <c r="W3" s="1"/>
       <c r="X3" s="1"/>
       <c r="Y3" s="1"/>
@@ -1124,32 +1146,75 @@
       <c r="DL3" s="1"/>
       <c r="DM3" s="1"/>
       <c r="DN3" s="1"/>
+      <c r="DO3" s="1"/>
     </row>
-    <row r="4" spans="1:118" x14ac:dyDescent="0.25">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
+    <row r="4" spans="1:119" x14ac:dyDescent="0.25">
+      <c r="A4" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="18">
+        <v>2</v>
+      </c>
+      <c r="C4" s="3">
+        <v>130</v>
+      </c>
+      <c r="D4" s="3">
+        <v>2026</v>
+      </c>
       <c r="E4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="3"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
-      <c r="N4" s="1"/>
-      <c r="O4" s="1"/>
-      <c r="P4" s="1"/>
-      <c r="Q4" s="1"/>
-      <c r="R4" s="1"/>
-      <c r="S4" s="1"/>
-      <c r="T4" s="1"/>
-      <c r="U4" s="5"/>
-      <c r="V4" s="1"/>
+      <c r="F4" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="G4" s="14">
+        <v>46081</v>
+      </c>
+      <c r="H4" s="13">
+        <v>46042</v>
+      </c>
+      <c r="I4" s="14">
+        <v>46096</v>
+      </c>
+      <c r="J4" s="13">
+        <v>46078</v>
+      </c>
+      <c r="K4" s="13">
+        <v>46083</v>
+      </c>
+      <c r="L4" s="1">
+        <v>18</v>
+      </c>
+      <c r="M4" s="1">
+        <v>4</v>
+      </c>
+      <c r="N4" s="13">
+        <v>46080</v>
+      </c>
+      <c r="O4" s="1">
+        <v>14</v>
+      </c>
+      <c r="P4" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="13">
+        <v>46042</v>
+      </c>
+      <c r="R4" s="1">
+        <v>10</v>
+      </c>
+      <c r="S4" s="1">
+        <v>0</v>
+      </c>
+      <c r="T4" s="13">
+        <v>46083</v>
+      </c>
+      <c r="U4" s="1">
+        <v>10</v>
+      </c>
+      <c r="V4" s="5">
+        <v>59</v>
+      </c>
       <c r="W4" s="1"/>
       <c r="X4" s="1"/>
       <c r="Y4" s="1"/>
@@ -1246,17 +1311,16 @@
       <c r="DL4" s="1"/>
       <c r="DM4" s="1"/>
       <c r="DN4" s="1"/>
+      <c r="DO4" s="1"/>
     </row>
-    <row r="5" spans="1:118" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:119" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
-      <c r="E5" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="F5" s="3"/>
-      <c r="G5" s="1"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="17"/>
+      <c r="G5" s="3"/>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
@@ -1270,8 +1334,8 @@
       <c r="R5" s="1"/>
       <c r="S5" s="1"/>
       <c r="T5" s="1"/>
-      <c r="U5" s="5"/>
-      <c r="V5" s="1"/>
+      <c r="U5" s="1"/>
+      <c r="V5" s="5"/>
       <c r="W5" s="1"/>
       <c r="X5" s="1"/>
       <c r="Y5" s="1"/>
@@ -1368,9 +1432,9 @@
       <c r="DL5" s="1"/>
       <c r="DM5" s="1"/>
       <c r="DN5" s="1"/>
+      <c r="DO5" s="1"/>
     </row>
-    <row r="6" spans="1:118" x14ac:dyDescent="0.25">
-      <c r="V6" s="1"/>
+    <row r="6" spans="1:119" x14ac:dyDescent="0.25">
       <c r="W6" s="1"/>
       <c r="X6" s="1"/>
       <c r="Y6" s="1"/>
@@ -1467,9 +1531,9 @@
       <c r="DL6" s="1"/>
       <c r="DM6" s="1"/>
       <c r="DN6" s="1"/>
+      <c r="DO6" s="1"/>
     </row>
-    <row r="7" spans="1:118" x14ac:dyDescent="0.25">
-      <c r="V7" s="1"/>
+    <row r="7" spans="1:119" x14ac:dyDescent="0.25">
       <c r="W7" s="1"/>
       <c r="X7" s="1"/>
       <c r="Y7" s="1"/>
@@ -1566,6 +1630,7 @@
       <c r="DL7" s="1"/>
       <c r="DM7" s="1"/>
       <c r="DN7" s="1"/>
+      <c r="DO7" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1587,48 +1652,48 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="D1" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="E1" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="F1" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="G1" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="H1" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="I1" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="J1" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="K1" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="J1" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="K1" s="7" t="s">
-        <v>30</v>
-      </c>
       <c r="L1" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="M1" s="10" t="s">
         <v>33</v>
-      </c>
-      <c r="M1" s="10" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B2" s="6">
         <v>6666101</v>
@@ -1652,7 +1717,7 @@
         <v>400920251740</v>
       </c>
       <c r="I2" s="8" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="J2" s="6">
         <v>11922025567</v>
@@ -1665,7 +1730,7 @@
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B3" s="6">
         <v>6666102</v>
@@ -1689,7 +1754,7 @@
         <v>400920251740</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="J3" s="6">
         <v>11922025160</v>
@@ -1704,7 +1769,7 @@
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B4" s="6">
         <v>6666103</v>
@@ -1728,7 +1793,7 @@
         <v>400920251740</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="J4" s="6">
         <v>11922025909</v>
@@ -1745,7 +1810,7 @@
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B5" s="6">
         <v>6666103</v>
@@ -1769,7 +1834,7 @@
         <v>400920251740</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="J5" s="6">
         <v>11922025121</v>
@@ -1784,7 +1849,7 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B6" s="6">
         <v>6666103</v>
@@ -1808,7 +1873,7 @@
         <v>400920251740</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="J6" s="6">
         <v>11922025909</v>
@@ -1823,7 +1888,7 @@
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B7" s="6">
         <v>6666103</v>
@@ -1847,7 +1912,7 @@
         <v>400920251740</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="J7" s="6">
         <v>11922025909</v>
@@ -1862,7 +1927,7 @@
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B8" s="6">
         <v>6666103</v>
@@ -1886,7 +1951,7 @@
         <v>400920251740</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="J8" s="6">
         <v>11922025909</v>
@@ -1901,7 +1966,7 @@
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B9" s="6">
         <v>6666103</v>
@@ -1925,7 +1990,7 @@
         <v>400920251740</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="J9" s="6">
         <v>11922025909</v>
@@ -1940,7 +2005,7 @@
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B10" s="6">
         <v>6666103</v>
@@ -1964,7 +2029,7 @@
         <v>400920251740</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="J10" s="6">
         <v>11922025909</v>
@@ -1979,7 +2044,7 @@
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B11" s="6">
         <v>6666103</v>
@@ -2003,7 +2068,7 @@
         <v>400920251740</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="J11" s="6">
         <v>11922025909</v>

--- a/Data/ON_Market.xlsx
+++ b/Data/ON_Market.xlsx
@@ -8,18 +8,29 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CBF37EA-F097-4D67-8B31-6C0A55136DBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B10D36E5-5A40-44AA-BBA6-828F86C106AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19725" windowHeight="11760" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settlement" sheetId="1" r:id="rId1"/>
     <sheet name="OnMarket" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -1156,7 +1167,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="3">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D4" s="3">
         <v>2026</v>
@@ -1696,7 +1707,7 @@
         <v>29</v>
       </c>
       <c r="B2" s="6">
-        <v>6666101</v>
+        <v>6666104</v>
       </c>
       <c r="C2" s="6">
         <v>9999996</v>
@@ -1720,12 +1731,14 @@
         <v>30</v>
       </c>
       <c r="J2" s="6">
-        <v>11922025567</v>
+        <v>11922026133</v>
       </c>
       <c r="K2" s="8">
-        <v>110001017786</v>
-      </c>
-      <c r="L2" s="1"/>
+        <v>110001032140</v>
+      </c>
+      <c r="L2" s="1">
+        <v>100</v>
+      </c>
       <c r="M2" s="1"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">

--- a/Data/ON_Market.xlsx
+++ b/Data/ON_Market.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B10D36E5-5A40-44AA-BBA6-828F86C106AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FD0984F-C3AE-403A-A15B-302A3E3D3D04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19725" windowHeight="11760" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="46">
   <si>
     <t>ExchangeMaster</t>
   </si>
@@ -172,6 +172,9 @@
   </si>
   <si>
     <t>COTTONBALES</t>
+  </si>
+  <si>
+    <t>sf</t>
   </si>
 </sst>
 </file>
@@ -1167,7 +1170,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="3">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D4" s="3">
         <v>2026</v>
@@ -1704,10 +1707,10 @@
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B2" s="6">
-        <v>6666104</v>
+        <v>32</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>45</v>
       </c>
       <c r="C2" s="6">
         <v>9999996</v>
@@ -1731,10 +1734,10 @@
         <v>30</v>
       </c>
       <c r="J2" s="6">
-        <v>11922026133</v>
+        <v>11922026134</v>
       </c>
       <c r="K2" s="8">
-        <v>110001032140</v>
+        <v>110001039632</v>
       </c>
       <c r="L2" s="1">
         <v>100</v>

--- a/Data/ON_Market.xlsx
+++ b/Data/ON_Market.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FD0984F-C3AE-403A-A15B-302A3E3D3D04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D28A4D89-0892-4B84-B1F0-B351897958A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19725" windowHeight="11760" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="46">
   <si>
     <t>ExchangeMaster</t>
   </si>
@@ -174,7 +174,7 @@
     <t>COTTONBALES</t>
   </si>
   <si>
-    <t>sf</t>
+    <t>c10092026</t>
   </si>
 </sst>
 </file>
@@ -1170,7 +1170,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="3">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D4" s="3">
         <v>2026</v>
@@ -1182,19 +1182,19 @@
         <v>44</v>
       </c>
       <c r="G4" s="14">
-        <v>46081</v>
+        <v>46170</v>
       </c>
       <c r="H4" s="13">
-        <v>46042</v>
+        <v>46101</v>
       </c>
       <c r="I4" s="14">
-        <v>46096</v>
+        <v>46127</v>
       </c>
       <c r="J4" s="13">
-        <v>46078</v>
+        <v>46103</v>
       </c>
       <c r="K4" s="13">
-        <v>46083</v>
+        <v>46167</v>
       </c>
       <c r="L4" s="1">
         <v>18</v>
@@ -1203,7 +1203,7 @@
         <v>4</v>
       </c>
       <c r="N4" s="13">
-        <v>46080</v>
+        <v>46169</v>
       </c>
       <c r="O4" s="1">
         <v>14</v>
@@ -1212,7 +1212,7 @@
         <v>0</v>
       </c>
       <c r="Q4" s="13">
-        <v>46042</v>
+        <v>46104</v>
       </c>
       <c r="R4" s="1">
         <v>10</v>
@@ -1221,7 +1221,7 @@
         <v>0</v>
       </c>
       <c r="T4" s="13">
-        <v>46083</v>
+        <v>46124</v>
       </c>
       <c r="U4" s="1">
         <v>10</v>
@@ -1709,32 +1709,32 @@
       <c r="A2" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B2" s="6" t="s">
-        <v>45</v>
+      <c r="B2" s="6">
+        <v>24032026</v>
       </c>
       <c r="C2" s="6">
-        <v>9999996</v>
+        <v>6656413</v>
       </c>
       <c r="D2" s="6">
-        <v>1000421</v>
+        <v>6539191</v>
       </c>
       <c r="E2" s="6">
         <v>15</v>
       </c>
       <c r="F2" s="8">
-        <v>100673000000011</v>
+        <v>120484000001272</v>
       </c>
       <c r="G2" s="6">
-        <v>973015</v>
+        <v>2026</v>
       </c>
       <c r="H2" s="8">
-        <v>400920251740</v>
+        <v>24032026</v>
       </c>
       <c r="I2" s="8" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="J2" s="6">
-        <v>11922026134</v>
+        <v>11022026135</v>
       </c>
       <c r="K2" s="8">
         <v>110001039632</v>
@@ -1825,276 +1825,108 @@
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="B5" s="6">
-        <v>6666103</v>
-      </c>
-      <c r="C5" s="6">
-        <v>9999996</v>
-      </c>
-      <c r="D5" s="6">
-        <v>1000421</v>
-      </c>
-      <c r="E5" s="6">
-        <v>1</v>
-      </c>
-      <c r="F5" s="8">
-        <v>100673000000011</v>
-      </c>
-      <c r="G5" s="6">
-        <v>973015</v>
-      </c>
-      <c r="H5" s="8">
-        <v>400920251740</v>
-      </c>
-      <c r="I5" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="J5" s="6">
-        <v>11922025121</v>
-      </c>
-      <c r="K5" s="15">
-        <v>110001031407</v>
-      </c>
-      <c r="L5" s="1">
-        <v>100</v>
-      </c>
+      <c r="A5" s="6"/>
+      <c r="B5" s="6"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="6"/>
+      <c r="K5" s="15"/>
+      <c r="L5" s="1"/>
       <c r="M5" s="1"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="B6" s="6">
-        <v>6666103</v>
-      </c>
-      <c r="C6" s="6">
-        <v>9999996</v>
-      </c>
-      <c r="D6" s="6">
-        <v>1000421</v>
-      </c>
-      <c r="E6" s="6">
-        <v>1</v>
-      </c>
-      <c r="F6" s="8">
-        <v>100673000000011</v>
-      </c>
-      <c r="G6" s="6">
-        <v>973015</v>
-      </c>
-      <c r="H6" s="8">
-        <v>400920251740</v>
-      </c>
-      <c r="I6" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="J6" s="6">
-        <v>11922025909</v>
-      </c>
-      <c r="K6" s="15">
-        <v>110001031506</v>
-      </c>
-      <c r="L6" s="1">
-        <v>100</v>
-      </c>
+      <c r="A6" s="6"/>
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="8"/>
+      <c r="J6" s="6"/>
+      <c r="K6" s="15"/>
+      <c r="L6" s="1"/>
       <c r="M6" s="1"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="B7" s="6">
-        <v>6666103</v>
-      </c>
-      <c r="C7" s="6">
-        <v>9999996</v>
-      </c>
-      <c r="D7" s="6">
-        <v>1000421</v>
-      </c>
-      <c r="E7" s="6">
-        <v>1</v>
-      </c>
-      <c r="F7" s="8">
-        <v>100673000000011</v>
-      </c>
-      <c r="G7" s="6">
-        <v>973015</v>
-      </c>
-      <c r="H7" s="8">
-        <v>400920251740</v>
-      </c>
-      <c r="I7" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="J7" s="6">
-        <v>11922025909</v>
-      </c>
-      <c r="K7" s="15">
-        <v>110001031480</v>
-      </c>
-      <c r="L7" s="1">
-        <v>100</v>
-      </c>
+      <c r="A7" s="6"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="15"/>
+      <c r="L7" s="1"/>
       <c r="M7" s="1"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="B8" s="6">
-        <v>6666103</v>
-      </c>
-      <c r="C8" s="6">
-        <v>9999996</v>
-      </c>
-      <c r="D8" s="6">
-        <v>1000421</v>
-      </c>
-      <c r="E8" s="6">
-        <v>1</v>
-      </c>
-      <c r="F8" s="8">
-        <v>100673000000011</v>
-      </c>
-      <c r="G8" s="6">
-        <v>973015</v>
-      </c>
-      <c r="H8" s="8">
-        <v>400920251740</v>
-      </c>
-      <c r="I8" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="J8" s="6">
-        <v>11922025909</v>
-      </c>
-      <c r="K8" s="15">
-        <v>110001031464</v>
-      </c>
-      <c r="L8" s="1">
-        <v>100</v>
-      </c>
+      <c r="A8" s="6"/>
+      <c r="B8" s="6"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="6"/>
+      <c r="K8" s="15"/>
+      <c r="L8" s="1"/>
       <c r="M8" s="1"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A9" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="B9" s="6">
-        <v>6666103</v>
-      </c>
-      <c r="C9" s="6">
-        <v>9999996</v>
-      </c>
-      <c r="D9" s="6">
-        <v>1000421</v>
-      </c>
-      <c r="E9" s="6">
-        <v>1</v>
-      </c>
-      <c r="F9" s="8">
-        <v>100673000000011</v>
-      </c>
-      <c r="G9" s="6">
-        <v>973015</v>
-      </c>
-      <c r="H9" s="8">
-        <v>400920251740</v>
-      </c>
-      <c r="I9" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="J9" s="6">
-        <v>11922025909</v>
-      </c>
-      <c r="K9" s="15">
-        <v>110001031449</v>
-      </c>
-      <c r="L9" s="1">
-        <v>100</v>
-      </c>
+      <c r="A9" s="6"/>
+      <c r="B9" s="6"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="6"/>
+      <c r="K9" s="15"/>
+      <c r="L9" s="1"/>
       <c r="M9" s="1"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A10" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="B10" s="6">
-        <v>6666103</v>
-      </c>
-      <c r="C10" s="6">
-        <v>9999996</v>
-      </c>
-      <c r="D10" s="6">
-        <v>1000421</v>
-      </c>
-      <c r="E10" s="6">
-        <v>1</v>
-      </c>
-      <c r="F10" s="8">
-        <v>100673000000011</v>
-      </c>
-      <c r="G10" s="6">
-        <v>973015</v>
-      </c>
-      <c r="H10" s="8">
-        <v>400920251740</v>
-      </c>
-      <c r="I10" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="J10" s="6">
-        <v>11922025909</v>
-      </c>
-      <c r="K10" s="15">
-        <v>110001031381</v>
-      </c>
-      <c r="L10" s="1">
-        <v>100</v>
-      </c>
+      <c r="A10" s="6"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="6"/>
+      <c r="K10" s="15"/>
+      <c r="L10" s="1"/>
       <c r="M10" s="1"/>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="B11" s="6">
-        <v>6666103</v>
-      </c>
-      <c r="C11" s="6">
-        <v>9999996</v>
-      </c>
-      <c r="D11" s="6">
-        <v>1000421</v>
-      </c>
-      <c r="E11" s="6">
-        <v>1</v>
-      </c>
-      <c r="F11" s="8">
-        <v>100673000000011</v>
-      </c>
-      <c r="G11" s="6">
-        <v>973015</v>
-      </c>
-      <c r="H11" s="8">
-        <v>400920251740</v>
-      </c>
-      <c r="I11" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="J11" s="6">
-        <v>11922025909</v>
-      </c>
-      <c r="K11" s="15">
-        <v>110001031423</v>
-      </c>
-      <c r="L11" s="1">
-        <v>100</v>
-      </c>
+      <c r="A11" s="6"/>
+      <c r="B11" s="6"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="6"/>
+      <c r="K11" s="15"/>
+      <c r="L11" s="1"/>
       <c r="M11" s="1"/>
     </row>
   </sheetData>
